--- a/Security-data/data/output/usenix_security_2025_us_institutions.xlsx
+++ b/Security-data/data/output/usenix_security_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E478"/>
+  <dimension ref="A1:E481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3367,7 +3367,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Changjiang Li</t>
+          <t>Wentao Guo 0005</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3375,22 +3375,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-PRSA: Prompt Stealing Attacks against Real-World Prompt Services.</t>
+          <t>USENIX_SECURITY-How Researchers De-Identify Data in Practice.</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sizhe Chen</t>
+          <t>Adam J. Aviv</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3398,22 +3398,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-StruQ: Defending Against Prompt Injection with Structured Queries.</t>
+          <t>USENIX_SECURITY-How Researchers De-Identify Data in Practice.</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>UC Berkeley</t>
+          <t>The George Washington University</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Julien Piet</t>
+          <t>Michelle L. Mazurek</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-StruQ: Defending Against Prompt Injection with Structured Queries.</t>
+          <t>USENIX_SECURITY-How Researchers De-Identify Data in Practice.</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>UC Berkeley</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Chawin Sitawarin</t>
+          <t>Changjiang Li</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3444,22 +3444,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-StruQ: Defending Against Prompt Injection with Structured Queries.</t>
+          <t>USENIX_SECURITY-PRSA: Prompt Stealing Attacks against Real-World Prompt Services.</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>UC Berkeley</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Mark Russinovich</t>
+          <t>Sizhe Chen</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Great, Now Write an Article About That: The Crescendo Multi-Turn LLM Jailbreak Attack.</t>
+          <t>USENIX_SECURITY-StruQ: Defending Against Prompt Injection with Structured Queries.</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -3475,14 +3475,14 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Microsoft Azure</t>
+          <t>UC Berkeley</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ahmed Salem 0001</t>
+          <t>Julien Piet</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Great, Now Write an Article About That: The Crescendo Multi-Turn LLM Jailbreak Attack.</t>
+          <t>USENIX_SECURITY-StruQ: Defending Against Prompt Injection with Structured Queries.</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -3498,14 +3498,14 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>UC Berkeley</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Ronen Eldan</t>
+          <t>Chawin Sitawarin</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Great, Now Write an Article About That: The Crescendo Multi-Turn LLM Jailbreak Attack.</t>
+          <t>USENIX_SECURITY-StruQ: Defending Against Prompt Injection with Structured Queries.</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -3521,14 +3521,14 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>UC Berkeley</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Yingjiu Li</t>
+          <t>Mark Russinovich</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SelfDefend: LLMs Can Defend Themselves against Jailbreaking in a Practical Manner.</t>
+          <t>USENIX_SECURITY-Great, Now Write an Article About That: The Crescendo Multi-Turn LLM Jailbreak Attack.</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>University of Oregon</t>
+          <t>Microsoft Azure</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Jason Kim 0007</t>
+          <t>Ahmed Salem 0001</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3559,22 +3559,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-FLOP: Breaking the Apple M3 CPU via False Load Output Predictions.</t>
+          <t>USENIX_SECURITY-Great, Now Write an Article About That: The Crescendo Multi-Turn LLM Jailbreak Attack.</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Microsoft</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jalen Chuang</t>
+          <t>Ronen Eldan</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3582,22 +3582,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-FLOP: Breaking the Apple M3 CPU via False Load Output Predictions.</t>
+          <t>USENIX_SECURITY-Great, Now Write an Article About That: The Crescendo Multi-Turn LLM Jailbreak Attack.</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Microsoft</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Yingjiu Li</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3605,22 +3605,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-FLOP: Breaking the Apple M3 CPU via False Load Output Predictions.</t>
+          <t>USENIX_SECURITY-SelfDefend: LLMs Can Defend Themselves against Jailbreaking in a Practical Manner.</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>University of Oregon</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Jason Kim 0007</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Privacy Audit as Bits Transmission: (Im)possibilities for Audit by One Run.</t>
+          <t>USENIX_SECURITY-FLOP: Breaking the Apple M3 CPU via False Load Output Predictions.</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Yu Wei 0007</t>
+          <t>Jalen Chuang</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-General-Purpose f-DP Estimation and Auditing in a Black-Box Setting.</t>
+          <t>USENIX_SECURITY-FLOP: Breaking the Apple M3 CPU via False Load Output Predictions.</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Vassilis Zikas</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-General-Purpose f-DP Estimation and Auditing in a Black-Box Setting.</t>
+          <t>USENIX_SECURITY-FLOP: Breaking the Apple M3 CPU via False Load Output Predictions.</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Andrés Fábrega</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3697,22 +3697,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Mitigating Injection Attacks against E2EE Applications via View-Based Partitioning.</t>
+          <t>USENIX_SECURITY-Privacy Audit as Bits Transmission: (Im)possibilities for Audit by One Run.</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Samuel Breckenridge</t>
+          <t>Yu Wei 0007</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3720,22 +3720,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Mitigating Injection Attacks against E2EE Applications via View-Based Partitioning.</t>
+          <t>USENIX_SECURITY-General-Purpose f-DP Estimation and Auditing in a Black-Box Setting.</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Armin Namavari</t>
+          <t>Vassilis Zikas</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3743,22 +3743,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Mitigating Injection Attacks against E2EE Applications via View-Based Partitioning.</t>
+          <t>USENIX_SECURITY-General-Purpose f-DP Estimation and Auditing in a Black-Box Setting.</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Thomas Ristenpart</t>
+          <t>Andrés Fábrega</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3770,18 +3770,18 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Cornell Tech</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Neil Gong 0001</t>
+          <t>Samuel Breckenridge</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: On Gradient Leakage in Federated Learning.</t>
+          <t>USENIX_SECURITY-Mitigating Injection Attacks against E2EE Applications via View-Based Partitioning.</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Department of Electrical and Computer Engineering, Duke University, USA</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Xiaolan Gu</t>
+          <t>Armin Namavari</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3812,22 +3812,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DP-BREM: Differentially-Private and Byzantine-Robust Federated Learning with Client Momentum.</t>
+          <t>USENIX_SECURITY-Mitigating Injection Attacks against E2EE Applications via View-Based Partitioning.</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ming Li 0003</t>
+          <t>Thomas Ristenpart</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3835,22 +3835,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DP-BREM: Differentially-Private and Byzantine-Robust Federated Learning with Client Momentum.</t>
+          <t>USENIX_SECURITY-Mitigating Injection Attacks against E2EE Applications via View-Based Partitioning.</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>Cornell Tech</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Li Xiong 0001</t>
+          <t>Neil Gong 0001</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DP-BREM: Differentially-Private and Byzantine-Robust Federated Learning with Client Momentum.</t>
+          <t>USENIX_SECURITY-SoK: On Gradient Leakage in Federated Learning.</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Department of Electrical and Computer Engineering, Duke University, USA</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Nick Nikiforakis</t>
+          <t>Xiaolan Gu</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3881,22 +3881,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Doubly Dangerous: Evading Phishing Reporting Systems by Leveraging Email Tracking Techniques.</t>
+          <t>USENIX_SECURITY-DP-BREM: Differentially-Private and Byzantine-Robust Federated Learning with Client Momentum.</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Fujiao Ji</t>
+          <t>Ming Li 0003</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3904,22 +3904,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Evaluating the Effectiveness and Robustness of Visual Similarity-based Phishing Detection Models.</t>
+          <t>USENIX_SECURITY-DP-BREM: Differentially-Private and Byzantine-Robust Federated Learning with Client Momentum.</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>University of Tennessee, Knoxville</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Kiho Lee</t>
+          <t>Li Xiong 0001</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3927,22 +3927,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Evaluating the Effectiveness and Robustness of Visual Similarity-based Phishing Detection Models.</t>
+          <t>USENIX_SECURITY-DP-BREM: Differentially-Private and Byzantine-Robust Federated Learning with Client Momentum.</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>University of Tennessee, Knoxville</t>
+          <t>Emory University</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Doowon Kim</t>
+          <t>Nick Nikiforakis</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3950,22 +3950,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Evaluating the Effectiveness and Robustness of Visual Similarity-based Phishing Detection Models.</t>
+          <t>USENIX_SECURITY-Doubly Dangerous: Evading Phishing Reporting Systems by Leveraging Email Tracking Techniques.</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>University of Tennessee, Knoxville</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Fujiao Ji</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Predictive Response Optimization: Using Reinforcement Learning to Fight Online Social Network Abuse.</t>
+          <t>USENIX_SECURITY-Evaluating the Effectiveness and Robustness of Visual Similarity-based Phishing Detection Models.</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -3981,14 +3981,14 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>University of Tennessee, Knoxville</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Geoffrey Goh</t>
+          <t>Kiho Lee</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Predictive Response Optimization: Using Reinforcement Learning to Fight Online Social Network Abuse.</t>
+          <t>USENIX_SECURITY-Evaluating the Effectiveness and Robustness of Visual Similarity-based Phishing Detection Models.</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -4004,14 +4004,14 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>University of Tennessee, Knoxville</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Yan Jiang</t>
+          <t>Doowon Kim</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4019,22 +4019,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Predictive Response Optimization: Using Reinforcement Learning to Fight Online Social Network Abuse.</t>
+          <t>USENIX_SECURITY-Evaluating the Effectiveness and Robustness of Visual Similarity-based Phishing Detection Models.</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>University of Tennessee, Knoxville</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ajay Gupta</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Jiaxuan Wang</t>
+          <t>Geoffrey Goh</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>David Freeman</t>
+          <t>Yan Jiang</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Francesco Dinuzzo</t>
+          <t>Ajay Gupta</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Yu-Jye Tung</t>
+          <t>Jiaxuan Wang</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4134,22 +4134,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Hercules Droidot and the murder on the JNI Express.</t>
+          <t>USENIX_SECURITY-Predictive Response Optimization: Using Reinforcement Learning to Fight Online Social Network Abuse.</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Jessy Ayala</t>
+          <t>David Freeman</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4157,22 +4157,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Hercules Droidot and the murder on the JNI Express.</t>
+          <t>USENIX_SECURITY-Predictive Response Optimization: Using Reinforcement Learning to Fight Online Social Network Abuse.</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Joshua Garcia</t>
+          <t>Francesco Dinuzzo</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4180,22 +4180,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Hercules Droidot and the murder on the JNI Express.</t>
+          <t>USENIX_SECURITY-Predictive Response Optimization: Using Reinforcement Learning to Fight Online Social Network Abuse.</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Johnny So</t>
+          <t>Yu-Jye Tung</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4203,22 +4203,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Lost in the Mists of Time: Expirations in DNS Footprints of Mobile Apps.</t>
+          <t>USENIX_SECURITY-Hercules Droidot and the murder on the JNI Express.</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Nick Nikiforakis</t>
+          <t>Jessy Ayala</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4226,22 +4226,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Lost in the Mists of Time: Expirations in DNS Footprints of Mobile Apps.</t>
+          <t>USENIX_SECURITY-Hercules Droidot and the murder on the JNI Express.</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Seny Kamara</t>
+          <t>Joshua Garcia</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4249,22 +4249,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-PolySys: an Algebraic Leakage Attack Engine.</t>
+          <t>USENIX_SECURITY-Hercules Droidot and the murder on the JNI Express.</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Brown University and MongoDB Research</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Andrew Park</t>
+          <t>Johnny So</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -4272,22 +4272,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-PolySys: an Algebraic Leakage Attack Engine.</t>
+          <t>USENIX_SECURITY-Lost in the Mists of Time: Expirations in DNS Footprints of Mobile Apps.</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University and MongoDB Research</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ryan Lehmkuhl</t>
+          <t>Nick Nikiforakis</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4295,22 +4295,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Distributional Private Information Retrieval.</t>
+          <t>USENIX_SECURITY-Lost in the Mists of Time: Expirations in DNS Footprints of Mobile Apps.</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Alexandra Henzinger</t>
+          <t>Seny Kamara</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Distributional Private Information Retrieval.</t>
+          <t>USENIX_SECURITY-PolySys: an Algebraic Leakage Attack Engine.</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -4326,14 +4326,14 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Brown University and MongoDB Research</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Henry Corrigan-Gibbs</t>
+          <t>Andrew Park</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4341,22 +4341,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Distributional Private Information Retrieval.</t>
+          <t>USENIX_SECURITY-PolySys: an Algebraic Leakage Attack Engine.</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Carnegie Mellon University and MongoDB Research</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Arka Rai Choudhuri</t>
+          <t>Ryan Lehmkuhl</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Practical Mempool Privacy via One-time Setup Batched Threshold Encryption.</t>
+          <t>USENIX_SECURITY-Distributional Private Information Retrieval.</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -4372,14 +4372,14 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Nexus</t>
+          <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sanjam Garg</t>
+          <t>Alexandra Henzinger</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Practical Mempool Privacy via One-time Setup Batched Threshold Encryption.</t>
+          <t>USENIX_SECURITY-Distributional Private Information Retrieval.</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -4395,14 +4395,14 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Mingyuan Wang 0001</t>
+          <t>Henry Corrigan-Gibbs</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4410,22 +4410,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Practical Mempool Privacy via One-time Setup Batched Threshold Encryption.</t>
+          <t>USENIX_SECURITY-Distributional Private Information Retrieval.</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>NYU Shanghai</t>
+          <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>John Kristoff</t>
+          <t>Arka Rai Choudhuri</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4433,22 +4433,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Assessing the Aftermath: the Effects of a Global Takedown against DDoS-for-hire Services.</t>
+          <t>USENIX_SECURITY-Practical Mempool Privacy via One-time Setup Batched Threshold Encryption.</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>Nexus</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Henry Birge-Lee</t>
+          <t>Sanjam Garg</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-BGP Vortex: Update Message Floods Can Create Internet Instabilities.</t>
+          <t>USENIX_SECURITY-Practical Mempool Privacy via One-time Setup Batched Threshold Encryption.</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -4464,14 +4464,14 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Giacomo Giuliari</t>
+          <t>Mingyuan Wang 0001</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4479,22 +4479,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-BGP Vortex: Update Message Floods Can Create Internet Instabilities.</t>
+          <t>USENIX_SECURITY-Practical Mempool Privacy via One-time Setup Batched Threshold Encryption.</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mysten Labs</t>
+          <t>NYU Shanghai</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Weitong Li</t>
+          <t>John Kristoff</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4502,22 +4502,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ImpROV: Measurement and Practical Mitigation of Collateral Damage in RPKI Route Origin Validation.</t>
+          <t>USENIX_SECURITY-Assessing the Aftermath: the Effects of a Global Takedown against DDoS-for-hire Services.</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Yuze Li</t>
+          <t>Henry Birge-Lee</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ImpROV: Measurement and Practical Mitigation of Collateral Damage in RPKI Route Origin Validation.</t>
+          <t>USENIX_SECURITY-BGP Vortex: Update Message Floods Can Create Internet Instabilities.</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -4533,14 +4533,14 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Taejoong Chung</t>
+          <t>Giacomo Giuliari</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ImpROV: Measurement and Practical Mitigation of Collateral Damage in RPKI Route Origin Validation.</t>
+          <t>USENIX_SECURITY-BGP Vortex: Update Message Floods Can Create Internet Instabilities.</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -4556,14 +4556,14 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Mysten Labs</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Joseph Spracklen</t>
+          <t>Weitong Li</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs.</t>
+          <t>USENIX_SECURITY-ImpROV: Measurement and Practical Mitigation of Collateral Damage in RPKI Route Origin Validation.</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -4579,14 +4579,14 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>University of Texas at San Antonio</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Raveen Wijewickrama</t>
+          <t>Yuze Li</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs.</t>
+          <t>USENIX_SECURITY-ImpROV: Measurement and Practical Mitigation of Collateral Damage in RPKI Route Origin Validation.</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -4602,14 +4602,14 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>University of Texas at San Antonio</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Anindya Maiti</t>
+          <t>Taejoong Chung</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4617,22 +4617,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs.</t>
+          <t>USENIX_SECURITY-ImpROV: Measurement and Practical Mitigation of Collateral Damage in RPKI Route Origin Validation.</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>University of Oklahoma</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Bimal Viswanath</t>
+          <t>Joseph Spracklen</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4644,18 +4644,18 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Texas at San Antonio</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Hao Chen 0003</t>
+          <t>Raveen Wijewickrama</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4663,22 +4663,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Make Agent Defeat Agent: Automatic Detection of Taint-Style Vulnerabilities in LLM-based Agents.</t>
+          <t>USENIX_SECURITY-We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs.</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>University of Texas at San Antonio</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Vitaly Shmatikov</t>
+          <t>Anindya Maiti</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4686,22 +4686,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Machine Against the RAG: Jamming Retrieval-Augmented Generation with Blocker Documents.</t>
+          <t>USENIX_SECURITY-We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs.</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cornell Tech</t>
+          <t>University of Oklahoma</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Xiaozhong Liu 0001</t>
+          <t>Bimal Viswanath</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -4709,22 +4709,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Topic-FlipRAG: Topic-Orientated Adversarial Opinion Manipulation Attacks to Retrieval-Augmented Generation Models.</t>
+          <t>USENIX_SECURITY-We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs.</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>S. Hrushikesh Bhupathiraju</t>
+          <t>Hao Chen 0003</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Sound of Interference: Electromagnetic Eavesdropping Attack on Digital Microphones Using Pulse Density Modulation.</t>
+          <t>USENIX_SECURITY-Make Agent Defeat Agent: Automatic Detection of Taint-Style Vulnerabilities in LLM-based Agents.</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>UC Davis</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Rishikesh Bhatt</t>
+          <t>Vitaly Shmatikov</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Sound of Interference: Electromagnetic Eavesdropping Attack on Digital Microphones Using Pulse Density Modulation.</t>
+          <t>USENIX_SECURITY-Machine Against the RAG: Jamming Retrieval-Augmented Generation with Blocker Documents.</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -4763,14 +4763,14 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Cornell Tech</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sara Rampazzi</t>
+          <t>Xiaozhong Liu 0001</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Sound of Interference: Electromagnetic Eavesdropping Attack on Digital Microphones Using Pulse Density Modulation.</t>
+          <t>USENIX_SECURITY-Topic-FlipRAG: Topic-Orientated Adversarial Opinion Manipulation Attacks to Retrieval-Augmented Generation Models.</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Haining Wang 0001</t>
+          <t>S. Hrushikesh Bhupathiraju</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4801,22 +4801,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TimeTravel: Real-time Timing Drift Attack on System Time Using Acoustic Waves.</t>
+          <t>USENIX_SECURITY-Sound of Interference: Electromagnetic Eavesdropping Attack on Digital Microphones Using Pulse Density Modulation.</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Junpeng Wan</t>
+          <t>Rishikesh Bhatt</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4824,22 +4824,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-HubBub: Contention-Based Side-Channel Attacks on USB Hubs.</t>
+          <t>USENIX_SECURITY-Sound of Interference: Electromagnetic Eavesdropping Attack on Digital Microphones Using Pulse Density Modulation.</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Han Gao</t>
+          <t>Sara Rampazzi</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4847,22 +4847,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-HubBub: Contention-Based Side-Channel Attacks on USB Hubs.</t>
+          <t>USENIX_SECURITY-Sound of Interference: Electromagnetic Eavesdropping Attack on Digital Microphones Using Pulse Density Modulation.</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Dave (Jing) Tian</t>
+          <t>Haining Wang 0001</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4870,22 +4870,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-HubBub: Contention-Based Side-Channel Attacks on USB Hubs.</t>
+          <t>USENIX_SECURITY-TimeTravel: Real-time Timing Drift Attack on System Time Using Acoustic Waves.</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Doguhan Yeke</t>
+          <t>Junpeng Wan</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
+          <t>USENIX_SECURITY-HubBub: Contention-Based Side-Channel Attacks on USB Hubs.</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -4908,7 +4908,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Muslum Ozgur Ozmen</t>
+          <t>Han Gao</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
+          <t>USENIX_SECURITY-HubBub: Contention-Based Side-Channel Attacks on USB Hubs.</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>James M. Goppert</t>
+          <t>Dave (Jing) Tian</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4939,11 +4939,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
+          <t>USENIX_SECURITY-HubBub: Contention-Based Side-Channel Attacks on USB Hubs.</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Inseok Hwang 0002</t>
+          <t>Doguhan Yeke</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Antonio Bianchi</t>
+          <t>Muslum Ozgur Ozmen</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4989,18 +4989,18 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>James M. Goppert</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Ruoyu Wu</t>
+          <t>Inseok Hwang 0002</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5031,11 +5031,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
+          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Muqi Zou</t>
+          <t>Antonio Bianchi</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5054,11 +5054,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
+          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Dongyan Xu</t>
+          <t>Z. Berkay Celik</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5077,11 +5077,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
+          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Dave (Jing) Tian</t>
+          <t>Ruoyu Wu</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Antonio Bianchi</t>
+          <t>Muqi Zou</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Yu Pan</t>
+          <t>Dongyan Xu</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5146,22 +5146,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
+          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Wanjing Han</t>
+          <t>Dave (Jing) Tian</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5169,22 +5169,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
+          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Mu Zhang 0001</t>
+          <t>Antonio Bianchi</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5192,22 +5192,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
+          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Tiantian Gong</t>
+          <t>Yu Pan</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
+          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -5223,14 +5223,14 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Gustavo Franco Camilo</t>
+          <t>Wanjing Han</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
+          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -5246,14 +5246,14 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Kartik Nayak</t>
+          <t>Mu Zhang 0001</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5261,22 +5261,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
+          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Aniket Kate</t>
+          <t>Tiantian Gong</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5288,18 +5288,18 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Purdue University and Supra Research</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Yuxin (Myles) Liu</t>
+          <t>Gustavo Franco Camilo</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5307,22 +5307,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
+          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Habiba Farrukh</t>
+          <t>Kartik Nayak</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5330,22 +5330,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
+          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Ardalan Amiri Sani</t>
+          <t>Aniket Kate</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5353,22 +5353,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
+          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>Purdue University and Supra Research</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Gene Tsudik</t>
+          <t>Yuxin (Myles) Liu</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Seongbin Park</t>
+          <t>Habiba Farrukh</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5399,22 +5399,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
+          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Alexander Vilesov</t>
+          <t>Ardalan Amiri Sani</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5422,22 +5422,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
+          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>UC Irvine</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Jinghuai Zhang</t>
+          <t>Gene Tsudik</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5445,22 +5445,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
+          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>UC Irvine</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Hossein Khalili</t>
+          <t>Seongbin Park</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Yuan Tian</t>
+          <t>Alexander Vilesov</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5495,18 +5495,18 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Achuta Kadambi</t>
+          <t>Jinghuai Zhang</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Nader Sehatbakhsh</t>
+          <t>Hossein Khalili</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Muhammad Shoaib</t>
+          <t>Yuan Tian</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5560,22 +5560,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
+          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>UCLA</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Alex Suh</t>
+          <t>Achuta Kadambi</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
+          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Wajih Ul Hassan</t>
+          <t>Nader Sehatbakhsh</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -5606,22 +5606,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
+          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Junming Chen</t>
+          <t>Muhammad Shoaib</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
+          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -5637,14 +5637,14 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Xiaoyue Ma</t>
+          <t>Alex Suh</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
+          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -5660,14 +5660,14 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Lannan Luo</t>
+          <t>Wajih Ul Hassan</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
+          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -5683,14 +5683,14 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Qiang Zeng 0001</t>
+          <t>Junming Chen</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Zheng Yu 0003</t>
+          <t>Xiaoyue Ma</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -5721,22 +5721,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
+          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Ziyi Guo</t>
+          <t>Lannan Luo</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5744,22 +5744,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
+          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Yuhang Wu 0003</t>
+          <t>Qiang Zeng 0001</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5767,22 +5767,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
+          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Jiahao Yu 0001</t>
+          <t>Zheng Yu 0003</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Yan Chen 0004</t>
+          <t>Ziyi Guo</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Xinyu Xing 0001</t>
+          <t>Yuhang Wu 0003</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Shouhuai Xu</t>
+          <t>Jiahao Yu 0001</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Automated Vulnerability Repair: Methods, Tools, and Assessments.</t>
+          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>University of Colorado Colorado Springs</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Ying Li 0095</t>
+          <t>Yan Chen 0004</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -5882,22 +5882,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
+          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Faysal Hossain Shezan</t>
+          <t>Xinyu Xing 0001</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5905,22 +5905,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
+          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>University of Texas at Arlington</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Bomin Wei</t>
+          <t>Shouhuai Xu</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
+          <t>USENIX_SECURITY-SoK: Automated Vulnerability Repair: Methods, Tools, and Assessments.</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>University of Colorado Colorado Springs</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Gang Wang 0011</t>
+          <t>Ying Li 0095</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5955,18 +5955,18 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Yuan Tian 0001</t>
+          <t>Faysal Hossain Shezan</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5978,18 +5978,18 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Haoran Yang 0002</t>
+          <t>Bomin Wei</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -5997,22 +5997,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-APPATCH: Automated Adaptive Prompting Large Language Models for Real-World Software Vulnerability Patching.</t>
+          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Washington State University</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Shiyu Sun</t>
+          <t>Gang Wang 0011</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6020,22 +6020,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
+          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Yunlong Xing</t>
+          <t>Yuan Tian 0001</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
+          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>UCLA</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Xinda Wang 0001</t>
+          <t>Haoran Yang 0002</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6066,22 +6066,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
+          <t>USENIX_SECURITY-APPATCH: Automated Adaptive Prompting Large Language Models for Real-World Software Vulnerability Patching.</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas</t>
+          <t>Washington State University</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Shu Wang 0004</t>
+          <t>Shiyu Sun</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6093,18 +6093,18 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>George Mason University and Palo Alto Networks, Inc.</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Kun Sun 0001</t>
+          <t>Yunlong Xing</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6116,7 +6116,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Hanqing Guo</t>
+          <t>Xinda Wang 0001</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
+          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>University of Hawaii at Mānoa</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Junfeng Guo</t>
+          <t>Shu Wang 0004</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
+          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>George Mason University and Palo Alto Networks, Inc.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Heng Huang 0001</t>
+          <t>Kun Sun 0001</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
+          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -6189,14 +6189,14 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ravishka Rathnasuriya</t>
+          <t>Hanqing Guo</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
+          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -6212,14 +6212,14 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of Hawaii at Mānoa</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Tingxi Li</t>
+          <t>Junfeng Guo</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
+          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -6235,14 +6235,14 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Zexin Xu</t>
+          <t>Heng Huang 0001</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6250,22 +6250,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
+          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Zihe Song</t>
+          <t>Ravishka Rathnasuriya</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Mirazul Haque</t>
+          <t>Tingxi Li</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Simin Chen</t>
+          <t>Zexin Xu</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Wei Yang 0013</t>
+          <t>Zihe Song</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Armin Sarabi</t>
+          <t>Mirazul Haque</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6365,22 +6365,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
+          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Ziyuan Huang 0004</t>
+          <t>Simin Chen</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6388,22 +6388,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
+          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Chenlan Wang 0001</t>
+          <t>Wei Yang 0013</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6411,22 +6411,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
+          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Tai Karir</t>
+          <t>Armin Sarabi</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Mingyan Liu</t>
+          <t>Ziyuan Huang 0004</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Sayak Saha Roy</t>
+          <t>Chenlan Wang 0001</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -6480,22 +6480,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
+          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Elham Pourabbas Vafa</t>
+          <t>Tai Karir</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -6503,22 +6503,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
+          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Shirin Nilizadeh</t>
+          <t>Mingyan Liu</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -6526,22 +6526,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
+          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Maurice Shih</t>
+          <t>Sayak Saha Roy</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
+          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -6557,14 +6557,14 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>University Of Maryland</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Michael Rosenberg</t>
+          <t>Elham Pourabbas Vafa</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
+          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -6580,14 +6580,14 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>University Of Maryland</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Hari Kailad</t>
+          <t>Shirin Nilizadeh</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
+          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>University Of Maryland</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Ian Miers</t>
+          <t>Maurice Shih</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -6622,18 +6622,18 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>University Of Maryland</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Zhengyao Lin</t>
+          <t>Michael Rosenberg</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -6641,22 +6641,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
+          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University Of Maryland</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Michael McLoughlin</t>
+          <t>Hari Kailad</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -6664,22 +6664,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
+          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University Of Maryland</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Pratap Singh</t>
+          <t>Ian Miers</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -6687,22 +6687,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
+          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Paul Hitchcox</t>
+          <t>Zhengyao Lin</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Joshua Gancher</t>
+          <t>Michael McLoughlin</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -6737,18 +6737,18 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Bryan Parno</t>
+          <t>Pratap Singh</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -6760,7 +6760,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Pratap Singh</t>
+          <t>Paul Hitchcox</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -6779,11 +6779,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
+          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -6802,11 +6802,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
+          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -6825,11 +6825,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
+          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Hans W. A. Hanley</t>
+          <t>Pratap Singh</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
+          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -6856,14 +6856,14 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Emily Okabe</t>
+          <t>Joshua Gancher</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
+          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -6879,14 +6879,14 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Zakir Durumeric</t>
+          <t>Bryan Parno</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
+          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -6902,14 +6902,14 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Catherine Han</t>
+          <t>Hans W. A. Hanley</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
+          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -6932,7 +6932,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Anne Li</t>
+          <t>Emily Okabe</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
+          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -6955,7 +6955,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Deepak Kumar 0006</t>
+          <t>Zakir Durumeric</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
+          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -6971,14 +6971,14 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Zakir Durumeric</t>
+          <t>Catherine Han</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Aditi Raghunathan</t>
+          <t>Anne Li</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vulnerability of Text-Matching in ML/AI Conference Reviewer Assignments to Collusions.</t>
+          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -7017,14 +7017,14 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Nihar B. Shah</t>
+          <t>Deepak Kumar 0006</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vulnerability of Text-Matching in ML/AI Conference Reviewer Assignments to Collusions.</t>
+          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -7040,14 +7040,14 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Madelyne Xiao</t>
+          <t>Zakir Durumeric</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -7055,22 +7055,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Machine Learning for Misinformation Detection.</t>
+          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Yingjiu Li</t>
+          <t>Aditi Raghunathan</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
+          <t>USENIX_SECURITY-Vulnerability of Text-Matching in ML/AI Conference Reviewer Assignments to Collusions.</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>University of Oregon</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Zilin Shen</t>
+          <t>Nihar B. Shah</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
+          <t>USENIX_SECURITY-Vulnerability of Text-Matching in ML/AI Conference Reviewer Assignments to Collusions.</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Imtiaz Karim</t>
+          <t>Madelyne Xiao</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -7124,22 +7124,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
+          <t>USENIX_SECURITY-SoK: Machine Learning for Misinformation Detection.</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Elisa Bertino</t>
+          <t>Yingjiu Li</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -7151,18 +7151,18 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Oregon</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Chaoshun Zuo</t>
+          <t>Zilin Shen</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Thorough Security Analysis of BLE Proximity Tracking Protocols.</t>
+          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Ohio State University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Maryam Motallebighomi</t>
+          <t>Imtiaz Karim</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -7193,22 +7193,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
+          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Jason Veara</t>
+          <t>Elisa Bertino</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
+          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Evangelos Bitsikas</t>
+          <t>Chaoshun Zuo</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
+          <t>USENIX_SECURITY-A Thorough Security Analysis of BLE Proximity Tracking Protocols.</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Aanjhan Ranganathan</t>
+          <t>Maryam Motallebighomi</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Irtaza Shahid</t>
+          <t>Jason Veara</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -7285,22 +7285,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-For Human Ears Only: Preventing Automated Monitoring on Voice Data.</t>
+          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Nirupam Roy</t>
+          <t>Evangelos Bitsikas</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -7308,22 +7308,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-For Human Ears Only: Preventing Automated Monitoring on Voice Data.</t>
+          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Mohamed Suliman 0002</t>
+          <t>Aanjhan Ranganathan</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -7331,22 +7331,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
+          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>IBM Research and Trinity College Dublin, The University of Dublin</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Anisa Halimi</t>
+          <t>Irtaza Shahid</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -7354,22 +7354,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
+          <t>USENIX_SECURITY-For Human Ears Only: Preventing Automated Monitoring on Voice Data.</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Swanand Ravindra Kadhe</t>
+          <t>Nirupam Roy</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -7377,22 +7377,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
+          <t>USENIX_SECURITY-For Human Ears Only: Preventing Automated Monitoring on Voice Data.</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Nathalie Baracaldo</t>
+          <t>Mohamed Suliman 0002</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -7404,18 +7404,18 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>IBM Research and Trinity College Dublin, The University of Dublin</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Nima Naderloui</t>
+          <t>Anisa Halimi</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -7423,22 +7423,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
+          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Shenao Yan</t>
+          <t>Swanand Ravindra Kadhe</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -7446,22 +7446,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
+          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Jie Fu 0003</t>
+          <t>Nathalie Baracaldo</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
+          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
         </is>
       </c>
       <c r="D307" t="n">
@@ -7477,14 +7477,14 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Wendy Hui Wang</t>
+          <t>Nima Naderloui</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -7496,18 +7496,18 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Yuan Hong 0001</t>
+          <t>Shenao Yan</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Juyang Bai</t>
+          <t>Jie Fu 0003</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -7538,22 +7538,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
+          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Chaitali Chakrabarti</t>
+          <t>Wendy Hui Wang</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
+          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
         </is>
       </c>
       <c r="D311" t="n">
@@ -7569,14 +7569,14 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Deliang Fan</t>
+          <t>Yuan Hong 0001</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -7584,22 +7584,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
+          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Flavien Solt</t>
+          <t>Juyang Bai</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -7607,22 +7607,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-McSee: Evaluating Advanced Rowhammer Attacks and Defenses via Automated DRAM Traffic Analysis.</t>
+          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>UC Berkeley</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Ravan Nazaraliyev</t>
+          <t>Chaitali Chakrabarti</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -7630,22 +7630,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Not so Refreshing: Attacking GPUs using RFM Rowhammer Mitigation.</t>
+          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Yicheng Zhang 0004</t>
+          <t>Deliang Fan</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -7653,22 +7653,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Not so Refreshing: Attacking GPUs using RFM Rowhammer Mitigation.</t>
+          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Nureddin Kamadan</t>
+          <t>Flavien Solt</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -7676,22 +7676,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
+          <t>USENIX_SECURITY-McSee: Evaluating Advanced Rowhammer Attacks and Defenses via Automated DRAM Traffic Analysis.</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>UC Berkeley</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Walter Wang</t>
+          <t>Ravan Nazaraliyev</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -7699,22 +7699,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
+          <t>USENIX_SECURITY-Not so Refreshing: Attacking GPUs using RFM Rowhammer Mitigation.</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Stephan van Schaik</t>
+          <t>Yicheng Zhang 0004</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -7722,22 +7722,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
+          <t>USENIX_SECURITY-Not so Refreshing: Attacking GPUs using RFM Rowhammer Mitigation.</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Christina Garman</t>
+          <t>Nureddin Kamadan</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -7749,18 +7749,18 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Walter Wang</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Ziqi Zhang</t>
+          <t>Stephan van Schaik</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-I Can Tell Your Secrets: Inferring Privacy Attributes from Mini-app Interaction History in Super-apps.</t>
+          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Yimin Chen 0004</t>
+          <t>Christina Garman</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -7814,22 +7814,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-EchoLLM: LLM-Augmented Acoustic Eavesdropping Attack on Bone Conduction Headphones with mmWave Radar.</t>
+          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>University of Massachusetts Lowell</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Florian Schaub</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -7837,22 +7837,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-How Transparent is Usable Privacy and Security Research? A Meta-Study on Current Research Transparency Practices.</t>
+          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Jabari Kwesi</t>
+          <t>Ziqi Zhang</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -7860,22 +7860,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
+          <t>USENIX_SECURITY-I Can Tell Your Secrets: Inferring Privacy Attributes from Mini-app Interaction History in Super-apps.</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Jiaxun Cao</t>
+          <t>Yimin Chen 0004</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -7883,22 +7883,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
+          <t>USENIX_SECURITY-EchoLLM: LLM-Augmented Acoustic Eavesdropping Attack on Bone Conduction Headphones with mmWave Radar.</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Massachusetts Lowell</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Riya Manchanda</t>
+          <t>Florian Schaub</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -7906,22 +7906,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
+          <t>USENIX_SECURITY-How Transparent is Usable Privacy and Security Research? A Meta-Study on Current Research Transparency Practices.</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Omer Akgul</t>
+          <t>Jabari Kwesi</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -7929,22 +7929,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Privacy Solution or Menace? Investigating Perceptions of Radio-Frequency Sensing.</t>
+          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>University of Maryland/Carnegie Mellon University</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Lorrie Faith Cranor</t>
+          <t>Jiaxun Cao</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -7952,22 +7952,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Privacy Solution or Menace? Investigating Perceptions of Radio-Frequency Sensing.</t>
+          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Yuxi Wu</t>
+          <t>Riya Manchanda</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -7975,22 +7975,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
+          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Ruoxi Zhang</t>
+          <t>Omer Akgul</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
+          <t>USENIX_SECURITY-Privacy Solution or Menace? Investigating Perceptions of Radio-Frequency Sensing.</t>
         </is>
       </c>
       <c r="D330" t="n">
@@ -8006,14 +8006,14 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Maryland/Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Shiyue Liu</t>
+          <t>Lorrie Faith Cranor</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -8021,11 +8021,11 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
+          <t>USENIX_SECURITY-Privacy Solution or Menace? Investigating Perceptions of Radio-Frequency Sensing.</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Mufei He</t>
+          <t>Yuxi Wu</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -8048,18 +8048,18 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Aidan Hong</t>
+          <t>Ruoxi Zhang</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Fei Fang 0001</t>
+          <t>Shiyue Liu</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Hong Shen 0004</t>
+          <t>Mufei He</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Yasemin Acar</t>
+          <t>Aidan Hong</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -8136,22 +8136,22 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Security and Privacy Advice for UPI Users in India.</t>
+          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Paderborn University and The George Washington University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Omer Akgul</t>
+          <t>Fei Fang 0001</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -8159,22 +8159,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
+          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>University of Maryland/Carnegie Mellon University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Richard Roberts</t>
+          <t>Hong Shen 0004</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -8182,22 +8182,22 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
+          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Emma Shroyer</t>
+          <t>Yasemin Acar</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
+          <t>USENIX_SECURITY-Security and Privacy Advice for UPI Users in India.</t>
         </is>
       </c>
       <c r="D339" t="n">
@@ -8213,14 +8213,14 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>Paderborn University and The George Washington University</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Dave Levin</t>
+          <t>Omer Akgul</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -8232,18 +8232,18 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>University of Maryland/Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Michelle L. Mazurek</t>
+          <t>Richard Roberts</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Qinge Xie</t>
+          <t>Emma Shroyer</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -8274,22 +8274,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Waltzz: WebAssembly Runtime Fuzzing with Stack-Invariant Transformation.</t>
+          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Yuan Tian 0001</t>
+          <t>Dave Levin</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -8297,22 +8297,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Waltzz: WebAssembly Runtime Fuzzing with Stack-Invariant Transformation.</t>
+          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Chaoshun Zuo</t>
+          <t>Michelle L. Mazurek</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-MBFuzzer: A Multi-Party Protocol Fuzzer for MQTT Brokers.</t>
+          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
         </is>
       </c>
       <c r="D344" t="n">
@@ -8328,14 +8328,14 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Ohio State University</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Chuyang Chen 0001</t>
+          <t>Qinge Xie</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -8343,22 +8343,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ELFuzz: Efficient Input Generation via LLM-driven Synthesis Over Fuzzer Space.</t>
+          <t>USENIX_SECURITY-Waltzz: WebAssembly Runtime Fuzzing with Stack-Invariant Transformation.</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Brendan Dolan-Gavitt</t>
+          <t>Yuan Tian 0001</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -8366,22 +8366,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ELFuzz: Efficient Input Generation via LLM-driven Synthesis Over Fuzzer Space.</t>
+          <t>USENIX_SECURITY-Waltzz: WebAssembly Runtime Fuzzing with Stack-Invariant Transformation.</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>UCLA</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Yupeng Yang</t>
+          <t>Chaoshun Zuo</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -8389,22 +8389,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
+          <t>USENIX_SECURITY-MBFuzzer: A Multi-Party Protocol Fuzzer for MQTT Brokers.</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Shenglong Yao</t>
+          <t>Chuyang Chen 0001</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -8412,22 +8412,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
+          <t>USENIX_SECURITY-ELFuzz: Efficient Input Generation via LLM-driven Synthesis Over Fuzzer Space.</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Jizhou Chen</t>
+          <t>Brendan Dolan-Gavitt</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
+          <t>USENIX_SECURITY-ELFuzz: Efficient Input Generation via LLM-driven Synthesis Over Fuzzer Space.</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Wenke Lee</t>
+          <t>Yupeng Yang</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Xiang Li</t>
+          <t>Shenglong Yao</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
+          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Ying Meng</t>
+          <t>Jizhou Chen</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -8504,22 +8504,22 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
+          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Junming Chen</t>
+          <t>Wenke Lee</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -8527,22 +8527,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
+          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Lannan Luo</t>
+          <t>Xiang Li</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Qiang Zeng 0001</t>
+          <t>Ying Meng</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Junming Chen</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Lifecycle Unlearning Commitment Management: Measuring Sample-level Unlearning Completeness.</t>
+          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Qinge Xie</t>
+          <t>Lannan Luo</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
+          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Karthik Ramakrishnan</t>
+          <t>Qiang Zeng 0001</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
+          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Frank Li 0001</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -8665,22 +8665,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
+          <t>USENIX_SECURITY-Towards Lifecycle Unlearning Commitment Management: Measuring Sample-level Unlearning Completeness.</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Jocelyn Wang</t>
+          <t>Qinge Xie</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -8688,22 +8688,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Websites' Global Privacy Control Compliance at Scale and over Time.</t>
+          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Julia Netter</t>
+          <t>Karthik Ramakrishnan</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -8711,22 +8711,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
+          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Tim Nelson</t>
+          <t>Frank Li 0001</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -8734,22 +8734,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
+          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Skyler Austen</t>
+          <t>Jocelyn Wang</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -8757,22 +8757,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
+          <t>USENIX_SECURITY-Websites' Global Privacy Control Compliance at Scale and over Time.</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Eva Lau</t>
+          <t>Julia Netter</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Colton Rusch</t>
+          <t>Tim Nelson</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Malte Schwarzkopf</t>
+          <t>Skyler Austen</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Kathi Fisler</t>
+          <t>Eva Lau</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Carolina Ortega Pérez</t>
+          <t>Colton Rusch</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -8872,22 +8872,22 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Encrypted Access Logging for Online Accounts: Device Attributions without Device Tracking.</t>
+          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Alaa Daffalla</t>
+          <t>Malte Schwarzkopf</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -8895,22 +8895,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Encrypted Access Logging for Online Accounts: Device Attributions without Device Tracking.</t>
+          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Yevgeniy Dodis</t>
+          <t>Kathi Fisler</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -8918,22 +8918,22 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-How to Compare Bandwidth Constrained Two-Party Secure Messaging Protocols: A Quest for A More Efficient and Secure Post-Quantum Protocol.</t>
+          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Daniel Jost 0001</t>
+          <t>Carolina Ortega Pérez</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-How to Compare Bandwidth Constrained Two-Party Secure Messaging Protocols: A Quest for A More Efficient and Secure Post-Quantum Protocol.</t>
+          <t>USENIX_SECURITY-Encrypted Access Logging for Online Accounts: Device Attributions without Device Tracking.</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Tongwei Ren</t>
+          <t>Alaa Daffalla</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -8964,22 +8964,22 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
+          <t>USENIX_SECURITY-Encrypted Access Logging for Online Accounts: Device Attributions without Device Tracking.</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Ronghan Che</t>
+          <t>Yevgeniy Dodis</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
+          <t>USENIX_SECURITY-How to Compare Bandwidth Constrained Two-Party Secure Messaging Protocols: A Quest for A More Efficient and Secure Post-Quantum Protocol.</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -8995,14 +8995,14 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Robert J. Walls</t>
+          <t>Daniel Jost 0001</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -9010,22 +9010,22 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
+          <t>USENIX_SECURITY-How to Compare Bandwidth Constrained Two-Party Secure Messaging Protocols: A Quest for A More Efficient and Secure Post-Quantum Protocol.</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Jay Bosamiya</t>
+          <t>Tongwei Ren</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
+          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -9041,14 +9041,14 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Microsoft Research</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Maverick Woo</t>
+          <t>Ronghan Che</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
+          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -9064,14 +9064,14 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Bryan Parno</t>
+          <t>Robert J. Walls</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -9079,22 +9079,22 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
+          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Yi Cai</t>
+          <t>Jay Bosamiya</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
+          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -9110,14 +9110,14 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Microsoft Research</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Pratap Singh</t>
+          <t>Maverick Woo</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
+          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -9140,7 +9140,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Zhengyao Lin</t>
+          <t>Bryan Parno</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
+          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -9163,7 +9163,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Jay Bosamiya</t>
+          <t>Yi Cai</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -9175,18 +9175,18 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Microsoft Research</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Joshua Gancher</t>
+          <t>Pratap Singh</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -9198,18 +9198,18 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Milijana Surbatovich</t>
+          <t>Zhengyao Lin</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -9221,18 +9221,18 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Bryan Parno</t>
+          <t>Jay Bosamiya</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -9244,18 +9244,18 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Microsoft Research</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Sai Ritvik Tanksalkar</t>
+          <t>Joshua Gancher</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -9263,22 +9263,22 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
+          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Siddharth Muralee</t>
+          <t>Milijana Surbatovich</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -9286,22 +9286,22 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
+          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Srihari Danduri</t>
+          <t>Bryan Parno</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -9309,22 +9309,22 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
+          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Antonio Bianchi</t>
+          <t>Sai Ritvik Tanksalkar</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>James C. Davis 0001</t>
+          <t>Siddharth Muralee</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Aravind Kumar Machiry</t>
+          <t>Srihari Danduri</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -9382,7 +9382,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Hung-Mao Chen</t>
+          <t>Antonio Bianchi</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -9401,22 +9401,22 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
+          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Xu He</t>
+          <t>James C. Davis 0001</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -9424,22 +9424,22 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
+          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Shu Wang 0004</t>
+          <t>Aravind Kumar Machiry</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -9447,22 +9447,22 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
+          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>George Mason University and Palo Alto Networks, Inc.</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Xiaokuan Zhang</t>
+          <t>Hung-Mao Chen</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Kun Sun 0001</t>
+          <t>Xu He</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Andrew Bao</t>
+          <t>Shu Wang 0004</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -9516,22 +9516,22 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
+          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>University of Minnesota, Twin Cities</t>
+          <t>George Mason University and Palo Alto Networks, Inc.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Stephen McCamant</t>
+          <t>Xiaokuan Zhang</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -9539,22 +9539,22 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
+          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>University of Minnesota, Twin Cities</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Pen-Chung Yew</t>
+          <t>Kun Sun 0001</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -9562,22 +9562,22 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
+          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>University of Minnesota, Twin Cities</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Murtuza Jadliwala</t>
+          <t>Andrew Bao</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -9585,22 +9585,22 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LightShed: Defeating Perturbation-based Image Copyright Protections.</t>
+          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>University of Texas at San Antonio</t>
+          <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Minhao Jin</t>
+          <t>Stephen McCamant</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -9608,22 +9608,22 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Robustifying ML-powered Network Classifiers with PANTS.</t>
+          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Maria Apostolaki</t>
+          <t>Pen-Chung Yew</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -9631,22 +9631,22 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Robustifying ML-powered Network Classifiers with PANTS.</t>
+          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Chenyi Wang 0005</t>
+          <t>Murtuza Jadliwala</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -9654,22 +9654,22 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
+          <t>USENIX_SECURITY-LightShed: Defeating Perturbation-based Image Copyright Protections.</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>University of Texas at San Antonio</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Raymond Muller</t>
+          <t>Minhao Jin</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -9677,22 +9677,22 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
+          <t>USENIX_SECURITY-Robustifying ML-powered Network Classifiers with PANTS.</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Ruoyu Song 0001</t>
+          <t>Maria Apostolaki</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -9700,22 +9700,22 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
+          <t>USENIX_SECURITY-Robustifying ML-powered Network Classifiers with PANTS.</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Jean-Philippe Monteuuis</t>
+          <t>Chenyi Wang 0005</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -9727,18 +9727,18 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Jonathan Petit</t>
+          <t>Raymond Muller</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -9750,18 +9750,18 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>Ruoyu Song 0001</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -9773,7 +9773,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Ming Li 0003</t>
+          <t>Jean-Philippe Monteuuis</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -9796,18 +9796,18 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>Qualcomm</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Jennifer Miller</t>
+          <t>Jonathan Petit</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Qualcomm</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Manas Ghandat</t>
+          <t>Z. Berkay Celik</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Kyle Zeng</t>
+          <t>Ming Li 0003</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -9861,22 +9861,22 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Hongkai Chen</t>
+          <t>Jennifer Miller</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Tiffany Bao</t>
+          <t>Manas Ghandat</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Ruoyu Wang 0001</t>
+          <t>Kyle Zeng</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -9934,7 +9934,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Adam Doupé</t>
+          <t>Hongkai Chen</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -9957,7 +9957,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Yan Shoshitaishvili</t>
+          <t>Tiffany Bao</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Yue Zhang 0025</t>
+          <t>Ruoyu Wang 0001</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -9999,22 +9999,22 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The Cost of Performance: Breaking ThreadX with Kernel Object Masquerading Attacks.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Drexel University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Xinwen Fu</t>
+          <t>Adam Doupé</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -10022,22 +10022,22 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The Cost of Performance: Breaking ThreadX with Kernel Object Masquerading Attacks.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>University of Massachusetts Lowell</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Wojciech Ozga</t>
+          <t>Yan Shoshitaishvili</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -10045,22 +10045,22 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Save what must be saved: Secure context switching with Sailor.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>IBM Research - Zurich</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Tianyao Gu</t>
+          <t>Yue Zhang 0025</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -10068,22 +10068,22 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
+          <t>USENIX_SECURITY-The Cost of Performance: Breaking ThreadX with Kernel Object Masquerading Attacks.</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
+          <t>Drexel University</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Afonso Tinoco</t>
+          <t>Xinwen Fu</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -10091,22 +10091,22 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
+          <t>USENIX_SECURITY-The Cost of Performance: Breaking ThreadX with Kernel Object Masquerading Attacks.</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
+          <t>University of Massachusetts Lowell</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Elaine Shi</t>
+          <t>Wojciech Ozga</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -10114,22 +10114,22 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
+          <t>USENIX_SECURITY-Save what must be saved: Secure context switching with Sailor.</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
+          <t>IBM Research - Zurich</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Xinwen Fu</t>
+          <t>Tianyao Gu</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -10137,22 +10137,22 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Distributed Private Aggregation in Graph Neural Networks.</t>
+          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>University of Massachusetts Lowell</t>
+          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>David Froelicher</t>
+          <t>Afonso Tinoco</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -10160,22 +10160,22 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
+          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Bonnie Berger</t>
+          <t>Elaine Shi</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -10183,22 +10183,22 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
+          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Hyunghoon Cho</t>
+          <t>Xinwen Fu</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -10206,22 +10206,22 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
+          <t>USENIX_SECURITY-Distributed Private Aggregation in Graph Neural Networks.</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of Massachusetts Lowell</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Mazharul Islam 0002</t>
+          <t>David Froelicher</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -10229,22 +10229,22 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
+          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>University of Wisconsin—Madison</t>
+          <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Sunpreet S. Arora</t>
+          <t>Bonnie Berger</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -10252,22 +10252,22 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
+          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Visa Research</t>
+          <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Rahul Chatterjee 0001</t>
+          <t>Hyunghoon Cho</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -10275,22 +10275,22 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
+          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>University of Wisconsin—Madison</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Ke Coby Wang</t>
+          <t>Mazharul Islam 0002</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -10302,18 +10302,18 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Visa Research</t>
+          <t>University of Wisconsin—Madison</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Alaa Daffalla</t>
+          <t>Sunpreet S. Arora</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -10321,22 +10321,22 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
+          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Visa Research</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Arkaprabha Bhattacharya</t>
+          <t>Rahul Chatterjee 0001</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -10344,22 +10344,22 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
+          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of Wisconsin—Madison</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Rahul Chatterjee 0001</t>
+          <t>Ke Coby Wang</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
+          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -10375,14 +10375,14 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>University of Wisconsin—Madison</t>
+          <t>Visa Research</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Nicola Dell</t>
+          <t>Alaa Daffalla</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -10394,18 +10394,18 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Cornell Tech</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Rosanna Bellini</t>
+          <t>Arkaprabha Bhattacharya</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -10417,18 +10417,18 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Thomas Ristenpart</t>
+          <t>Rahul Chatterjee 0001</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -10440,18 +10440,18 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Cornell Tech</t>
+          <t>University of Wisconsin—Madison</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Yuchen Yang 0001</t>
+          <t>Nicola Dell</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -10459,22 +10459,22 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
+          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>The Johns Hopkins University</t>
+          <t>Cornell Tech</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Qichang Liu</t>
+          <t>Rosanna Bellini</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -10482,22 +10482,22 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
+          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>The Johns Hopkins University</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Huan Zhang 0001</t>
+          <t>Thomas Ristenpart</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -10505,22 +10505,22 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
+          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>University of Illinois at Urbana–Champaign</t>
+          <t>Cornell Tech</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Yuchen Yang 0001</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -10532,18 +10532,18 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>The Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Gene Tsudik</t>
+          <t>Qichang Liu</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -10551,22 +10551,22 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Oblivious Digital Tokens.</t>
+          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>The Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>John Y. Kim</t>
+          <t>Huan Zhang 0001</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -10574,22 +10574,22 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
+          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>University of Illinois at Urbana–Champaign</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Chaoshun Zuo</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -10597,22 +10597,22 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
+          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Ohio State University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Gene Tsudik</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -10620,22 +10620,22 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
+          <t>USENIX_SECURITY-Oblivious Digital Tokens.</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>UC Irvine</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Grace Jia</t>
+          <t>John Y. Kim</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
+          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -10651,14 +10651,14 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Alex Wong 0001</t>
+          <t>Chaoshun Zuo</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
+          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
         </is>
       </c>
       <c r="D446" t="n">
@@ -10674,14 +10674,14 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Anurag Khandelwal</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -10689,22 +10689,22 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
+          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Yash Vekaria</t>
+          <t>Grace Jia</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
+          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
         </is>
       </c>
       <c r="D448" t="n">
@@ -10720,14 +10720,14 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Jonathan Levitsky</t>
+          <t>Alex Wong 0001</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -10735,22 +10735,22 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
+          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Zubair Shafiq</t>
+          <t>Anurag Khandelwal</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -10758,22 +10758,22 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
+          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Kaiyuan Zhang 0002</t>
+          <t>Yash Vekaria</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
         </is>
       </c>
       <c r="D451" t="n">
@@ -10789,14 +10789,14 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>UC Davis</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Siyuan Cheng 0005</t>
+          <t>Jonathan Levitsky</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -10804,22 +10804,22 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>UC Davis</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Hanxi Guo</t>
+          <t>Zubair Shafiq</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -10827,22 +10827,22 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>UC Davis</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Yuetian Chen</t>
+          <t>Kaiyuan Zhang 0002</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Zian Su</t>
+          <t>Siyuan Cheng 0005</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -10877,7 +10877,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Shengwei An</t>
+          <t>Hanxi Guo</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Yuntao Du 0002</t>
+          <t>Yuetian Chen</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Xiangyu Zhang 0001</t>
+          <t>Zian Su</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -10946,7 +10946,7 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Ninghui Li 0001</t>
+          <t>Shengwei An</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -10969,7 +10969,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Leo Marchyok</t>
+          <t>Yuntao Du 0002</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -10988,22 +10988,22 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Private Investigator: Extracting Personally Identifiable Information from Large Language Models Using Optimized Prompts.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Sanghyun Hong 0001</t>
+          <t>Xiangyu Zhang 0001</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -11011,22 +11011,22 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Private Investigator: Extracting Personally Identifiable Information from Large Language Models Using Optimized Prompts.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Zhengyu Liu</t>
+          <t>Ninghui Li 0001</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -11034,22 +11034,22 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Theo Lee</t>
+          <t>Leo Marchyok</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -11057,22 +11057,22 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
+          <t>USENIX_SECURITY-Private Investigator: Extracting Personally Identifiable Information from Large Language Models Using Optimized Prompts.</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Oregon State University</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Jianjia Yu</t>
+          <t>Sanghyun Hong 0001</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -11080,22 +11080,22 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
+          <t>USENIX_SECURITY-Private Investigator: Extracting Personally Identifiable Information from Large Language Models Using Optimized Prompts.</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Oregon State University</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Zifeng Kang</t>
+          <t>Zhengyu Liu</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -11107,7 +11107,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Theo Lee</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Jianjia Yu</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -11149,11 +11149,11 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Careless Retention and Management: Understanding and Detecting Data Retention Denial-of-Service Vulnerabilities in Java Web Containers.</t>
+          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Zifeng Kang</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -11172,11 +11172,11 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Automatic Detection and Exploitation of Java Web Application Vulnerabilities via Concolic Execution guided by Cross-thread Object Manipulation.</t>
+          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Yunhao Wang</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -11195,22 +11195,22 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Qelect: Lattice-based Single Secret Leader Election Made Practical.</t>
+          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Fan Zhang</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -11218,22 +11218,22 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Qelect: Lattice-based Single Secret Leader Election Made Practical.</t>
+          <t>USENIX_SECURITY-Careless Retention and Management: Understanding and Detecting Data Retention Denial-of-Service Vulnerabilities in Java Web Containers.</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Lakshmi Likhitha Mankali</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -11241,22 +11241,22 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+          <t>USENIX_SECURITY-Towards Automatic Detection and Exploitation of Java Web Application Vulnerabilities via Concolic Execution guided by Cross-thread Object Manipulation.</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Tandon School of Engineering, New York University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Mohammed Nabeel 0001</t>
+          <t>Yunhao Wang</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -11264,22 +11264,22 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+          <t>USENIX_SECURITY-Qelect: Lattice-based Single Secret Leader Election Made Practical.</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Tandon School of Engineering, New York University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Faiq Raees</t>
+          <t>Fan Zhang</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -11287,22 +11287,22 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+          <t>USENIX_SECURITY-Qelect: Lattice-based Single Secret Leader Election Made Practical.</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Michail Maniatakos</t>
+          <t>Lakshmi Likhitha Mankali</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -11314,18 +11314,18 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Tandon School of Engineering, New York University</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Ozgur Sinanoglu</t>
+          <t>Mohammed Nabeel 0001</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -11337,18 +11337,18 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Tandon School of Engineering, New York University</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Johann Knechtel</t>
+          <t>Faiq Raees</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -11360,18 +11360,18 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Apostolos Mavrogiannakis</t>
+          <t>Michail Maniatakos</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -11379,36 +11379,105 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-OBLIVIATOR: OBLIVIous Parallel Joins and other OperATORs in Shared Memory Environments.</t>
+          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
+          <t>Ozgur Sinanoglu</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>4</v>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>New York University Abu Dhabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Johann Knechtel</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>5</v>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>New York University Abu Dhabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Apostolos Mavrogiannakis</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-OBLIVIATOR: OBLIVIous Parallel Joins and other OperATORs in Shared Memory Environments.</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>0</v>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>University of California, Santa Cruz</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
           <t>Ioannis Demertzis</t>
         </is>
       </c>
-      <c r="B478" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C478" t="inlineStr">
+      <c r="B481" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C481" t="inlineStr">
         <is>
           <t>USENIX_SECURITY-OBLIVIATOR: OBLIVIous Parallel Joins and other OperATORs in Shared Memory Environments.</t>
         </is>
       </c>
-      <c r="D478" t="n">
+      <c r="D481" t="n">
         <v>2</v>
       </c>
-      <c r="E478" t="inlineStr">
+      <c r="E481" t="inlineStr">
         <is>
           <t>University of California, Santa Cruz</t>
         </is>

--- a/Security-data/data/output/usenix_security_2025_us_institutions.xlsx
+++ b/Security-data/data/output/usenix_security_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E481"/>
+  <dimension ref="A1:E482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11210,7 +11210,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Rigel Gjomemo</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -11218,15 +11218,15 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Careless Retention and Management: Understanding and Detecting Data Retention Denial-of-Service Vulnerabilities in Java Web Containers.</t>
+          <t>USENIX_SECURITY-FIXX: FInding eXploits from eXamples.</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
     </row>
@@ -11241,11 +11241,11 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Automatic Detection and Exploitation of Java Web Application Vulnerabilities via Concolic Execution guided by Cross-thread Object Manipulation.</t>
+          <t>USENIX_SECURITY-Careless Retention and Management: Understanding and Detecting Data Retention Denial-of-Service Vulnerabilities in Java Web Containers.</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Yunhao Wang</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -11264,22 +11264,22 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Qelect: Lattice-based Single Secret Leader Election Made Practical.</t>
+          <t>USENIX_SECURITY-Towards Automatic Detection and Exploitation of Java Web Application Vulnerabilities via Concolic Execution guided by Cross-thread Object Manipulation.</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Fan Zhang</t>
+          <t>Yunhao Wang</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -11291,7 +11291,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Lakshmi Likhitha Mankali</t>
+          <t>Fan Zhang</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -11310,22 +11310,22 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+          <t>USENIX_SECURITY-Qelect: Lattice-based Single Secret Leader Election Made Practical.</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Tandon School of Engineering, New York University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Mohammed Nabeel 0001</t>
+          <t>Lakshmi Likhitha Mankali</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -11337,7 +11337,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Faiq Raees</t>
+          <t>Mohammed Nabeel 0001</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -11360,18 +11360,18 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Tandon School of Engineering, New York University</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Michail Maniatakos</t>
+          <t>Faiq Raees</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -11383,18 +11383,18 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Ozgur Sinanoglu</t>
+          <t>Michail Maniatakos</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Johann Knechtel</t>
+          <t>Ozgur Sinanoglu</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -11429,7 +11429,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Apostolos Mavrogiannakis</t>
+          <t>Johann Knechtel</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -11448,36 +11448,59 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-OBLIVIATOR: OBLIVIous Parallel Joins and other OperATORs in Shared Memory Environments.</t>
+          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>New York University Abu Dhabi</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
+          <t>Apostolos Mavrogiannakis</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-OBLIVIATOR: OBLIVIous Parallel Joins and other OperATORs in Shared Memory Environments.</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>0</v>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>University of California, Santa Cruz</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
           <t>Ioannis Demertzis</t>
         </is>
       </c>
-      <c r="B481" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C481" t="inlineStr">
+      <c r="B482" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C482" t="inlineStr">
         <is>
           <t>USENIX_SECURITY-OBLIVIATOR: OBLIVIous Parallel Joins and other OperATORs in Shared Memory Environments.</t>
         </is>
       </c>
-      <c r="D481" t="n">
+      <c r="D482" t="n">
         <v>2</v>
       </c>
-      <c r="E481" t="inlineStr">
+      <c r="E482" t="inlineStr">
         <is>
           <t>University of California, Santa Cruz</t>
         </is>

--- a/Security-data/data/output/usenix_security_2025_us_institutions.xlsx
+++ b/Security-data/data/output/usenix_security_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E482"/>
+  <dimension ref="A1:E496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,7 +4471,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mingyuan Wang 0001</t>
+          <t>Guru-Vamsi Policharla</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4483,18 +4483,18 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>NYU Shanghai</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>John Kristoff</t>
+          <t>Mingyuan Wang 0001</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Assessing the Aftermath: the Effects of a Global Takedown against DDoS-for-hire Services.</t>
+          <t>USENIX_SECURITY-Practical Mempool Privacy via One-time Setup Batched Threshold Encryption.</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -4510,14 +4510,14 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>NYU Shanghai</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Henry Birge-Lee</t>
+          <t>John Kristoff</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-BGP Vortex: Update Message Floods Can Create Internet Instabilities.</t>
+          <t>USENIX_SECURITY-Assessing the Aftermath: the Effects of a Global Takedown against DDoS-for-hire Services.</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Giacomo Giuliari</t>
+          <t>Henry Birge-Lee</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4552,18 +4552,18 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Mysten Labs</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Weitong Li</t>
+          <t>Giacomo Giuliari</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4571,22 +4571,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ImpROV: Measurement and Practical Mitigation of Collateral Damage in RPKI Route Origin Validation.</t>
+          <t>USENIX_SECURITY-BGP Vortex: Update Message Floods Can Create Internet Instabilities.</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Mysten Labs</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Yuze Li</t>
+          <t>Weitong Li</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Taejoong Chung</t>
+          <t>Yuze Li</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Joseph Spracklen</t>
+          <t>Taejoong Chung</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4640,22 +4640,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs.</t>
+          <t>USENIX_SECURITY-ImpROV: Measurement and Practical Mitigation of Collateral Damage in RPKI Route Origin Validation.</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>University of Texas at San Antonio</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Raveen Wijewickrama</t>
+          <t>Joseph Spracklen</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Anindya Maiti</t>
+          <t>Raveen Wijewickrama</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4690,18 +4690,18 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>University of Oklahoma</t>
+          <t>University of Texas at San Antonio</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Bimal Viswanath</t>
+          <t>A. H. M. Nazmus Sakib</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -4713,18 +4713,18 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Texas at San Antonio</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Hao Chen 0003</t>
+          <t>Anindya Maiti</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Make Agent Defeat Agent: Automatic Detection of Taint-Style Vulnerabilities in LLM-based Agents.</t>
+          <t>USENIX_SECURITY-We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs.</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>University of Oklahoma</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Vitaly Shmatikov</t>
+          <t>Bimal Viswanath</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -4755,22 +4755,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Machine Against the RAG: Jamming Retrieval-Augmented Generation with Blocker Documents.</t>
+          <t>USENIX_SECURITY-We Have a Package for You! A Comprehensive Analysis of Package Hallucinations by Code Generating LLMs.</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Cornell Tech</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Xiaozhong Liu 0001</t>
+          <t>Hao Chen 0003</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Topic-FlipRAG: Topic-Orientated Adversarial Opinion Manipulation Attacks to Retrieval-Augmented Generation Models.</t>
+          <t>USENIX_SECURITY-Make Agent Defeat Agent: Automatic Detection of Taint-Style Vulnerabilities in LLM-based Agents.</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>UC Davis</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>S. Hrushikesh Bhupathiraju</t>
+          <t>Vitaly Shmatikov</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4801,22 +4801,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Sound of Interference: Electromagnetic Eavesdropping Attack on Digital Microphones Using Pulse Density Modulation.</t>
+          <t>USENIX_SECURITY-Machine Against the RAG: Jamming Retrieval-Augmented Generation with Blocker Documents.</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Cornell Tech</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Rishikesh Bhatt</t>
+          <t>Xiaozhong Liu 0001</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4824,22 +4824,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Sound of Interference: Electromagnetic Eavesdropping Attack on Digital Microphones Using Pulse Density Modulation.</t>
+          <t>USENIX_SECURITY-Topic-FlipRAG: Topic-Orientated Adversarial Opinion Manipulation Attacks to Retrieval-Augmented Generation Models.</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Sara Rampazzi</t>
+          <t>S. Hrushikesh Bhupathiraju</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Haining Wang 0001</t>
+          <t>Rishikesh Bhatt</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TimeTravel: Real-time Timing Drift Attack on System Time Using Acoustic Waves.</t>
+          <t>USENIX_SECURITY-Sound of Interference: Electromagnetic Eavesdropping Attack on Digital Microphones Using Pulse Density Modulation.</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -4878,14 +4878,14 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Junpeng Wan</t>
+          <t>Sara Rampazzi</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4893,22 +4893,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-HubBub: Contention-Based Side-Channel Attacks on USB Hubs.</t>
+          <t>USENIX_SECURITY-Sound of Interference: Electromagnetic Eavesdropping Attack on Digital Microphones Using Pulse Density Modulation.</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Han Gao</t>
+          <t>Haining Wang 0001</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-HubBub: Contention-Based Side-Channel Attacks on USB Hubs.</t>
+          <t>USENIX_SECURITY-TimeTravel: Real-time Timing Drift Attack on System Time Using Acoustic Waves.</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Dave (Jing) Tian</t>
+          <t>Junpeng Wan</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Doguhan Yeke</t>
+          <t>Han Gao</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4962,11 +4962,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
+          <t>USENIX_SECURITY-HubBub: Contention-Based Side-Channel Attacks on USB Hubs.</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Muslum Ozgur Ozmen</t>
+          <t>Dave (Jing) Tian</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4985,22 +4985,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
+          <t>USENIX_SECURITY-HubBub: Contention-Based Side-Channel Attacks on USB Hubs.</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>James M. Goppert</t>
+          <t>Doguhan Yeke</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Inseok Hwang 0002</t>
+          <t>Kartik Anand Pant</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Antonio Bianchi</t>
+          <t>Muslum Ozgur Ozmen</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5058,18 +5058,18 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>James M. Goppert</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5081,7 +5081,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Ruoyu Wu</t>
+          <t>Inseok Hwang 0002</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5100,11 +5100,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
+          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Muqi Zou</t>
+          <t>Antonio Bianchi</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5123,11 +5123,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
+          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Dongyan Xu</t>
+          <t>Z. Berkay Celik</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5146,11 +5146,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
+          <t>USENIX_SECURITY-Automated Discovery of Semantic Attacks in Multi-Robot Navigation Systems.</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Dave (Jing) Tian</t>
+          <t>Ruoyu Wu</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Antonio Bianchi</t>
+          <t>Muqi Zou</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Yu Pan</t>
+          <t>Dongyan Xu</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5215,22 +5215,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
+          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Wanjing Han</t>
+          <t>Dave (Jing) Tian</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5238,22 +5238,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
+          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Mu Zhang 0001</t>
+          <t>Antonio Bianchi</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5261,22 +5261,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
+          <t>USENIX_SECURITY-NeuroScope: Reverse Engineering Deep Neural Network on Edge Devices using Dynamic Analysis.</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Tiantian Gong</t>
+          <t>Yu Pan</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
+          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -5292,14 +5292,14 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Gustavo Franco Camilo</t>
+          <t>Wanjing Han</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
+          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -5315,14 +5315,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Kartik Nayak</t>
+          <t>Mu Zhang 0001</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5330,22 +5330,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
+          <t>USENIX_SECURITY-CollisionRepair: First-Aid and Automated Patching for Storage Collision Vulnerabilities in Smart Contracts.</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Aniket Kate</t>
+          <t>Tiantian Gong</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5357,18 +5357,18 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Purdue University and Supra Research</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Yuxin (Myles) Liu</t>
+          <t>Gustavo Franco Camilo</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5376,22 +5376,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
+          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Habiba Farrukh</t>
+          <t>Kartik Nayak</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5399,22 +5399,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
+          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Ardalan Amiri Sani</t>
+          <t>Aniket Kate</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5422,22 +5422,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
+          <t>USENIX_SECURITY-Recover from Excessive Faults in Partially-Synchronous BFT SMR.</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>Purdue University and Supra Research</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Gene Tsudik</t>
+          <t>Yuxin (Myles) Liu</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Seongbin Park</t>
+          <t>Habiba Farrukh</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5468,22 +5468,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
+          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Alexander Vilesov</t>
+          <t>Ardalan Amiri Sani</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5491,22 +5491,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
+          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>UC Irvine</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Jinghuai Zhang</t>
+          <t>Gene Tsudik</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5514,22 +5514,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
+          <t>USENIX_SECURITY-Scoop: Mitigation of Recapture Attacks on Provenance-Based Media Authentication.</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>UC Irvine</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Hossein Khalili</t>
+          <t>Seongbin Park</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Yuan Tian</t>
+          <t>Alexander Vilesov</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5564,18 +5564,18 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Achuta Kadambi</t>
+          <t>Jinghuai Zhang</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Nader Sehatbakhsh</t>
+          <t>Hossein Khalili</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Muhammad Shoaib</t>
+          <t>Yuan Tian</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -5629,22 +5629,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
+          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>UCLA</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Alex Suh</t>
+          <t>Achuta Kadambi</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -5652,22 +5652,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
+          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Wajih Ul Hassan</t>
+          <t>Nader Sehatbakhsh</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -5675,22 +5675,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
+          <t>USENIX_SECURITY-Chimera: Creating Digitally Signed Fake Photos by Fooling Image Recapture and Deepfake Detectors.</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Junming Chen</t>
+          <t>Muhammad Shoaib</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
+          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -5706,14 +5706,14 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Xiaoyue Ma</t>
+          <t>Alex Suh</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
+          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -5729,14 +5729,14 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Lannan Luo</t>
+          <t>Wajih Ul Hassan</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
+          <t>USENIX_SECURITY-Principled and Automated Approach for Investigating AR/VR Attacks.</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -5752,14 +5752,14 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Qiang Zeng 0001</t>
+          <t>Junming Chen</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Zheng Yu 0003</t>
+          <t>Xiaoyue Ma</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5790,22 +5790,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
+          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Ziyi Guo</t>
+          <t>Lannan Luo</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5813,22 +5813,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
+          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Yuhang Wu 0003</t>
+          <t>Qiang Zeng 0001</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5836,22 +5836,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
+          <t>USENIX_SECURITY-Tracking You from a Thousand Miles Away! Turning a Bluetooth Device into an Apple AirTag Without Root Privileges.</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Jiahao Yu 0001</t>
+          <t>Zheng Yu 0003</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Yan Chen 0004</t>
+          <t>Ziyi Guo</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Xinyu Xing 0001</t>
+          <t>Yuhang Wu 0003</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Shouhuai Xu</t>
+          <t>Jiahao Yu 0001</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Automated Vulnerability Repair: Methods, Tools, and Assessments.</t>
+          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>University of Colorado Colorado Springs</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Ying Li 0095</t>
+          <t>Yan Chen 0004</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5951,22 +5951,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
+          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Faysal Hossain Shezan</t>
+          <t>Xinyu Xing 0001</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5974,22 +5974,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
+          <t>USENIX_SECURITY-PATCHAGENT: A Practical Program Repair Agent Mimicking Human Expertise.</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>University of Texas at Arlington</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Bomin Wei</t>
+          <t>Shouhuai Xu</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -5997,22 +5997,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
+          <t>USENIX_SECURITY-SoK: Automated Vulnerability Repair: Methods, Tools, and Assessments.</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>University of Colorado Colorado Springs</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Gang Wang 0011</t>
+          <t>Ying Li 0095</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6024,18 +6024,18 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Yuan Tian 0001</t>
+          <t>Faysal Hossain Shezan</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6047,18 +6047,18 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Haoran Yang 0002</t>
+          <t>Bomin Wei</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6066,22 +6066,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-APPATCH: Automated Adaptive Prompting Large Language Models for Real-World Software Vulnerability Patching.</t>
+          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Washington State University</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Shiyu Sun</t>
+          <t>Gang Wang 0011</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
+          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Yunlong Xing</t>
+          <t>Yuan Tian 0001</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6112,22 +6112,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
+          <t>USENIX_SECURITY-SoK: Towards Effective Automated Vulnerability Repair.</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>UCLA</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Xinda Wang 0001</t>
+          <t>Haoran Yang 0002</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
+          <t>USENIX_SECURITY-APPATCH: Automated Adaptive Prompting Large Language Models for Real-World Software Vulnerability Patching.</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas</t>
+          <t>Washington State University</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Shu Wang 0004</t>
+          <t>Shiyu Sun</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6162,18 +6162,18 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>George Mason University and Palo Alto Networks, Inc.</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Kun Sun 0001</t>
+          <t>Yunlong Xing</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Hanqing Guo</t>
+          <t>Xinda Wang 0001</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6204,22 +6204,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
+          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>University of Hawaii at Mānoa</t>
+          <t>University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Junfeng Guo</t>
+          <t>Shu Wang 0004</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6227,22 +6227,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
+          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>George Mason University and Palo Alto Networks, Inc.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Heng Huang 0001</t>
+          <t>Kun Sun 0001</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
+          <t>USENIX_SECURITY-DISPATCH: Unraveling Security Patches from Entangled Code Changes.</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -6258,14 +6258,14 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Ravishka Rathnasuriya</t>
+          <t>Hanqing Guo</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
+          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -6281,14 +6281,14 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of Hawaii at Mānoa</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Tingxi Li</t>
+          <t>Junfeng Guo</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
+          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -6304,14 +6304,14 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Zexin Xu</t>
+          <t>Heng Huang 0001</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
+          <t>USENIX_SECURITY-AUDIO WATERMARK: Dynamic and Harmless Watermark for Black-box Voice Dataset Copyright Protection.</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Zihe Song</t>
+          <t>Ravishka Rathnasuriya</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Mirazul Haque</t>
+          <t>Tingxi Li</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Simin Chen</t>
+          <t>Zexin Xu</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Wei Yang 0013</t>
+          <t>Zihe Song</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Armin Sarabi</t>
+          <t>Mirazul Haque</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
+          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Ziyuan Huang 0004</t>
+          <t>Simin Chen</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6457,22 +6457,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
+          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Chenlan Wang 0001</t>
+          <t>Wei Yang 0013</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -6480,22 +6480,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
+          <t>USENIX_SECURITY-SoK: Efficiency Robustness of Dynamic Deep Learning Systems.</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Tai Karir</t>
+          <t>Armin Sarabi</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Mingyan Liu</t>
+          <t>Ziyuan Huang 0004</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Sayak Saha Roy</t>
+          <t>Chenlan Wang 0001</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -6549,22 +6549,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
+          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Elham Pourabbas Vafa</t>
+          <t>Tai Karir</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -6572,22 +6572,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
+          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Shirin Nilizadeh</t>
+          <t>Mingyan Liu</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
+          <t>USENIX_SECURITY-The Ransomware Decade: The Creation of a Fine-Grained Dataset and a Longitudinal Study.</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Maurice Shih</t>
+          <t>Sayak Saha Roy</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
+          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -6626,14 +6626,14 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>University Of Maryland</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Michael Rosenberg</t>
+          <t>Elham Pourabbas Vafa</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
+          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -6649,14 +6649,14 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>University Of Maryland</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Hari Kailad</t>
+          <t>Shirin Nilizadeh</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -6664,22 +6664,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
+          <t>USENIX_SECURITY-DarkGram: A Large-Scale Analysis of Cybercriminal Activity Channels on Telegram.</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>University Of Maryland</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Ian Miers</t>
+          <t>Nael B. Abu-Ghazaleh</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -6687,22 +6687,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
+          <t>USENIX_SECURITY-Secure Caches for Compartmentalized Software.</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Zhengyao Lin</t>
+          <t>Maurice Shih</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
+          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -6718,14 +6718,14 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University Of Maryland</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Michael McLoughlin</t>
+          <t>Michael Rosenberg</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
+          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -6741,14 +6741,14 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University Of Maryland</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Pratap Singh</t>
+          <t>Hari Kailad</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
+          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -6764,14 +6764,14 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University Of Maryland</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Paul Hitchcox</t>
+          <t>Ian Miers</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -6779,22 +6779,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
+          <t>USENIX_SECURITY-zk-promises: Anonymous Moderation, Reputation, and Blocking from Anonymous Credentials with Callbacks.</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Joshua Gancher</t>
+          <t>Zhengyao Lin</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -6806,18 +6806,18 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Bryan Parno</t>
+          <t>Michael McLoughlin</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -6848,11 +6848,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
+          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Joshua Gancher</t>
+          <t>Paul Hitchcox</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -6871,22 +6871,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
+          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Bryan Parno</t>
+          <t>Joshua Gancher</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -6894,22 +6894,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
+          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Hans W. A. Hanley</t>
+          <t>Bryan Parno</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -6917,22 +6917,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
+          <t>USENIX_SECURITY-Towards Practical, End-to-End Formally Verified X.509 Certificate Validators with Verdict.</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Emily Okabe</t>
+          <t>Pratap Singh</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
+          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Zakir Durumeric</t>
+          <t>Joshua Gancher</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -6963,22 +6963,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
+          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Catherine Han</t>
+          <t>Bryan Parno</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -6986,22 +6986,22 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
+          <t>USENIX_SECURITY-OwlC: Compiling Security Protocols to Verified, Secure, High-Performance Libraries.</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Anne Li</t>
+          <t>Hans W. A. Hanley</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -7009,11 +7009,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
+          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Deepak Kumar 0006</t>
+          <t>Emily Okabe</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -7032,15 +7032,15 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
+          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
@@ -7055,11 +7055,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
+          <t>USENIX_SECURITY-Tracking the Takes and Trajectories of English-Language News Narratives across Trustworthy and Worrisome Websites.</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Aditi Raghunathan</t>
+          <t>Catherine Han</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vulnerability of Text-Matching in ML/AI Conference Reviewer Assignments to Collusions.</t>
+          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Nihar B. Shah</t>
+          <t>Anne Li</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vulnerability of Text-Matching in ML/AI Conference Reviewer Assignments to Collusions.</t>
+          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Madelyne Xiao</t>
+          <t>Deepak Kumar 0006</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -7124,22 +7124,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SoK: Machine Learning for Misinformation Detection.</t>
+          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Yingjiu Li</t>
+          <t>Zakir Durumeric</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -7147,22 +7147,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
+          <t>USENIX_SECURITY-Characterizing the MrDeepFakes Sexual Deepfake Marketplace.</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>University of Oregon</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Zilin Shen</t>
+          <t>Jhih-Yi Hsieh</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
+          <t>USENIX_SECURITY-Vulnerability of Text-Matching in ML/AI Conference Reviewer Assignments to Collusions.</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Imtiaz Karim</t>
+          <t>Aditi Raghunathan</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -7193,22 +7193,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
+          <t>USENIX_SECURITY-Vulnerability of Text-Matching in ML/AI Conference Reviewer Assignments to Collusions.</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Elisa Bertino</t>
+          <t>Nihar B. Shah</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
+          <t>USENIX_SECURITY-Vulnerability of Text-Matching in ML/AI Conference Reviewer Assignments to Collusions.</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Chaoshun Zuo</t>
+          <t>Madelyne Xiao</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Thorough Security Analysis of BLE Proximity Tracking Protocols.</t>
+          <t>USENIX_SECURITY-SoK: Machine Learning for Misinformation Detection.</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Ohio State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Maryam Motallebighomi</t>
+          <t>Jonathan R. Mayer</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -7262,22 +7262,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
+          <t>USENIX_SECURITY-SoK: Machine Learning for Misinformation Detection.</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Jason Veara</t>
+          <t>Yingjiu Li</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -7285,22 +7285,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
+          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Oregon</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Evangelos Bitsikas</t>
+          <t>Zilin Shen</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -7308,22 +7308,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
+          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Aanjhan Ranganathan</t>
+          <t>Imtiaz Karim</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -7331,22 +7331,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
+          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Irtaza Shahid</t>
+          <t>Elisa Bertino</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -7354,22 +7354,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-For Human Ears Only: Preventing Automated Monitoring on Voice Data.</t>
+          <t>USENIX_SECURITY-AKMA+: Security and Privacy-Enhanced and Standard-Compatible AKMA for 5G Communication.</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Nirupam Roy</t>
+          <t>Chaoshun Zuo</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-For Human Ears Only: Preventing Automated Monitoring on Voice Data.</t>
+          <t>USENIX_SECURITY-A Thorough Security Analysis of BLE Proximity Tracking Protocols.</t>
         </is>
       </c>
       <c r="D303" t="n">
@@ -7385,14 +7385,14 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Mohamed Suliman 0002</t>
+          <t>Maryam Motallebighomi</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
+          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
         </is>
       </c>
       <c r="D304" t="n">
@@ -7408,14 +7408,14 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>IBM Research and Trinity College Dublin, The University of Dublin</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Anisa Halimi</t>
+          <t>Jason Veara</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
+          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
         </is>
       </c>
       <c r="D305" t="n">
@@ -7431,14 +7431,14 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Swanand Ravindra Kadhe</t>
+          <t>Evangelos Bitsikas</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
+          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -7454,14 +7454,14 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Nathalie Baracaldo</t>
+          <t>Aanjhan Ranganathan</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
+          <t>USENIX_SECURITY-eSIMplicity or eSIMplification? Privacy and Security Risks in the eSIM Ecosystem.</t>
         </is>
       </c>
       <c r="D307" t="n">
@@ -7477,14 +7477,14 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>IBM Research</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Nima Naderloui</t>
+          <t>Irtaza Shahid</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
+          <t>USENIX_SECURITY-For Human Ears Only: Preventing Automated Monitoring on Voice Data.</t>
         </is>
       </c>
       <c r="D308" t="n">
@@ -7500,14 +7500,14 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Shenao Yan</t>
+          <t>Nirupam Roy</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
+          <t>USENIX_SECURITY-For Human Ears Only: Preventing Automated Monitoring on Voice Data.</t>
         </is>
       </c>
       <c r="D309" t="n">
@@ -7523,14 +7523,14 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Jie Fu 0003</t>
+          <t>Mohamed Suliman 0002</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -7538,22 +7538,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
+          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>IBM Research and Trinity College Dublin, The University of Dublin</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Wendy Hui Wang</t>
+          <t>Anisa Halimi</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -7561,22 +7561,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
+          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Yuan Hong 0001</t>
+          <t>Swanand Ravindra Kadhe</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -7584,22 +7584,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
+          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Juyang Bai</t>
+          <t>Nathalie Baracaldo</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -7607,22 +7607,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
+          <t>USENIX_SECURITY-Towards a Re-evaluation of Data Forging Attacks in Practice.</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>IBM Research</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Chaitali Chakrabarti</t>
+          <t>Nima Naderloui</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -7630,22 +7630,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
+          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Deliang Fan</t>
+          <t>Shenao Yan</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -7653,22 +7653,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
+          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Flavien Solt</t>
+          <t>Jie Fu 0003</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -7676,22 +7676,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-McSee: Evaluating Advanced Rowhammer Attacks and Defenses via Automated DRAM Traffic Analysis.</t>
+          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>UC Berkeley</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Ravan Nazaraliyev</t>
+          <t>Wendy Hui Wang</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -7699,22 +7699,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Not so Refreshing: Attacking GPUs using RFM Rowhammer Mitigation.</t>
+          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Yicheng Zhang 0004</t>
+          <t>Yuan Hong 0001</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -7722,22 +7722,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Not so Refreshing: Attacking GPUs using RFM Rowhammer Mitigation.</t>
+          <t>USENIX_SECURITY-Rectifying Privacy and Efficacy Measurements in Machine Unlearning: A New Inference Attack Perspective.</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Nureddin Kamadan</t>
+          <t>Juyang Bai</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
+          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
         </is>
       </c>
       <c r="D319" t="n">
@@ -7753,14 +7753,14 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Walter Wang</t>
+          <t>Chaitali Chakrabarti</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -7768,22 +7768,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
+          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Stephan van Schaik</t>
+          <t>Deliang Fan</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
+          <t>USENIX_SECURITY-Phantom: Privacy-Preserving Deep Neural Network Model Obfuscation in Heterogeneous TEE and GPU System.</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Christina Garman</t>
+          <t>Flavien Solt</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -7814,22 +7814,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
+          <t>USENIX_SECURITY-McSee: Evaluating Advanced Rowhammer Attacks and Defenses via Automated DRAM Traffic Analysis.</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>UC Berkeley</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Ravan Nazaraliyev</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -7837,22 +7837,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
+          <t>USENIX_SECURITY-Not so Refreshing: Attacking GPUs using RFM Rowhammer Mitigation.</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Ziqi Zhang</t>
+          <t>Yicheng Zhang 0004</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-I Can Tell Your Secrets: Inferring Privacy Attributes from Mini-app Interaction History in Super-apps.</t>
+          <t>USENIX_SECURITY-Not so Refreshing: Attacking GPUs using RFM Rowhammer Mitigation.</t>
         </is>
       </c>
       <c r="D324" t="n">
@@ -7868,14 +7868,14 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Yimin Chen 0004</t>
+          <t>Nael B. Abu-Ghazaleh</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -7883,22 +7883,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-EchoLLM: LLM-Augmented Acoustic Eavesdropping Attack on Bone Conduction Headphones with mmWave Radar.</t>
+          <t>USENIX_SECURITY-Not so Refreshing: Attacking GPUs using RFM Rowhammer Mitigation.</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>University of Massachusetts Lowell</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Florian Schaub</t>
+          <t>Nureddin Kamadan</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -7906,22 +7906,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-How Transparent is Usable Privacy and Security Research? A Meta-Study on Current Research Transparency Practices.</t>
+          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Jabari Kwesi</t>
+          <t>Walter Wang</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -7929,22 +7929,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
+          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Jiaxun Cao</t>
+          <t>Stephan van Schaik</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -7952,22 +7952,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
+          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Riya Manchanda</t>
+          <t>Christina Garman</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -7975,22 +7975,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
+          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Omer Akgul</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -7998,22 +7998,22 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Privacy Solution or Menace? Investigating Perceptions of Radio-Frequency Sensing.</t>
+          <t>USENIX_SECURITY-ECC.fail: Mounting Rowhammer Attacks on DDR4 Servers with ECC Memory.</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>University of Maryland/Carnegie Mellon University</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Lorrie Faith Cranor</t>
+          <t>Ziqi Zhang</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -8021,22 +8021,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Privacy Solution or Menace? Investigating Perceptions of Radio-Frequency Sensing.</t>
+          <t>USENIX_SECURITY-I Can Tell Your Secrets: Inferring Privacy Attributes from Mini-app Interaction History in Super-apps.</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Yuxi Wu</t>
+          <t>Yimin Chen 0004</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -8044,22 +8044,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
+          <t>USENIX_SECURITY-EchoLLM: LLM-Augmented Acoustic Eavesdropping Attack on Bone Conduction Headphones with mmWave Radar.</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Massachusetts Lowell</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Ruoxi Zhang</t>
+          <t>Florian Schaub</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -8067,22 +8067,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
+          <t>USENIX_SECURITY-How Transparent is Usable Privacy and Security Research? A Meta-Study on Current Research Transparency Practices.</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Shiyue Liu</t>
+          <t>Jabari Kwesi</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -8090,22 +8090,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
+          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Mufei He</t>
+          <t>Jiaxun Cao</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -8113,22 +8113,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
+          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Aidan Hong</t>
+          <t>Riya Manchanda</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -8136,22 +8136,22 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
+          <t>USENIX_SECURITY-Exploring User Security and Privacy Attitudes and Concerns Toward the Use of General-Purpose LLM Chatbots for Mental Health.</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Fei Fang 0001</t>
+          <t>Omer Akgul</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -8159,22 +8159,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
+          <t>USENIX_SECURITY-Privacy Solution or Menace? Investigating Perceptions of Radio-Frequency Sensing.</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Maryland/Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Hong Shen 0004</t>
+          <t>Lorrie Faith Cranor</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -8182,11 +8182,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
+          <t>USENIX_SECURITY-Privacy Solution or Menace? Investigating Perceptions of Radio-Frequency Sensing.</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Yasemin Acar</t>
+          <t>Yuxi Wu</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -8205,22 +8205,22 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Security and Privacy Advice for UPI Users in India.</t>
+          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Paderborn University and The George Washington University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Omer Akgul</t>
+          <t>Ruoxi Zhang</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -8228,22 +8228,22 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
+          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>University of Maryland/Carnegie Mellon University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Richard Roberts</t>
+          <t>Shiyue Liu</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -8251,22 +8251,22 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
+          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Emma Shroyer</t>
+          <t>Mufei He</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -8274,22 +8274,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
+          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Dave Levin</t>
+          <t>Aidan Hong</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -8297,22 +8297,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
+          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Michelle L. Mazurek</t>
+          <t>Fei Fang 0001</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
+          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Qinge Xie</t>
+          <t>Hong Shen 0004</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -8343,22 +8343,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Waltzz: WebAssembly Runtime Fuzzing with Stack-Invariant Transformation.</t>
+          <t>USENIX_SECURITY-Navigating Security and Privacy Threats in Homeless Service Provision.</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Yuan Tian 0001</t>
+          <t>Yasemin Acar</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -8366,22 +8366,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Waltzz: WebAssembly Runtime Fuzzing with Stack-Invariant Transformation.</t>
+          <t>USENIX_SECURITY-Security and Privacy Advice for UPI Users in India.</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Paderborn University and The George Washington University</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Chaoshun Zuo</t>
+          <t>Omer Akgul</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -8389,22 +8389,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-MBFuzzer: A Multi-Party Protocol Fuzzer for MQTT Brokers.</t>
+          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Ohio State University</t>
+          <t>University of Maryland/Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Chuyang Chen 0001</t>
+          <t>Richard Roberts</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -8412,22 +8412,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ELFuzz: Efficient Input Generation via LLM-driven Synthesis Over Fuzzer Space.</t>
+          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Brendan Dolan-Gavitt</t>
+          <t>Emma Shroyer</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-ELFuzz: Efficient Input Generation via LLM-driven Synthesis Over Fuzzer Space.</t>
+          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Yupeng Yang</t>
+          <t>Dave Levin</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -8458,22 +8458,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
+          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Shenglong Yao</t>
+          <t>Michelle L. Mazurek</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
+          <t>USENIX_SECURITY-As Advertised? Understanding the Impact of Influencer VPN Ads.</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Maryland</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Jizhou Chen</t>
+          <t>Qinge Xie</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -8504,11 +8504,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
+          <t>USENIX_SECURITY-Waltzz: WebAssembly Runtime Fuzzing with Stack-Invariant Transformation.</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Wenke Lee</t>
+          <t>Yuan Tian 0001</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -8527,22 +8527,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
+          <t>USENIX_SECURITY-Waltzz: WebAssembly Runtime Fuzzing with Stack-Invariant Transformation.</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>UCLA</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Xiang Li</t>
+          <t>Chaoshun Zuo</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -8550,22 +8550,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
+          <t>USENIX_SECURITY-MBFuzzer: A Multi-Party Protocol Fuzzer for MQTT Brokers.</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Ying Meng</t>
+          <t>Chuyang Chen 0001</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -8573,22 +8573,22 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
+          <t>USENIX_SECURITY-ELFuzz: Efficient Input Generation via LLM-driven Synthesis Over Fuzzer Space.</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Junming Chen</t>
+          <t>Brendan Dolan-Gavitt</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
+          <t>USENIX_SECURITY-ELFuzz: Efficient Input Generation via LLM-driven Synthesis Over Fuzzer Space.</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Lannan Luo</t>
+          <t>Yupeng Yang</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
+          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Qiang Zeng 0001</t>
+          <t>Shenglong Yao</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
+          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Jizhou Chen</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -8665,22 +8665,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Lifecycle Unlearning Commitment Management: Measuring Sample-level Unlearning Completeness.</t>
+          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Qinge Xie</t>
+          <t>Wenke Lee</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
+          <t>USENIX_SECURITY-Hybrid Language Processor Fuzzing via LLM-Based Constraint Solving.</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Karthik Ramakrishnan</t>
+          <t>Xiang Li</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -8711,22 +8711,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
+          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Frank Li 0001</t>
+          <t>Ying Meng</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -8734,22 +8734,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
+          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Jocelyn Wang</t>
+          <t>Junming Chen</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -8757,22 +8757,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Websites' Global Privacy Control Compliance at Scale and over Time.</t>
+          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Julia Netter</t>
+          <t>Lannan Luo</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -8780,22 +8780,22 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
+          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Tim Nelson</t>
+          <t>Qiang Zeng 0001</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -8803,22 +8803,22 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
+          <t>USENIX_SECURITY-Rowhammer-Based Trojan Injection: One Bit Flip Is Sufficient for Backdooring DNNs.</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Skyler Austen</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -8826,22 +8826,22 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
+          <t>USENIX_SECURITY-Towards Lifecycle Unlearning Commitment Management: Measuring Sample-level Unlearning Completeness.</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Eva Lau</t>
+          <t>Qinge Xie</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -8849,22 +8849,22 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
+          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Colton Rusch</t>
+          <t>Karthik Ramakrishnan</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -8872,22 +8872,22 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
+          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Malte Schwarzkopf</t>
+          <t>Frank Li 0001</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -8895,22 +8895,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
+          <t>USENIX_SECURITY-Evaluating Privacy Policies under Modern Privacy Laws At Scale: An LLM-Based Automated Approach.</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Kathi Fisler</t>
+          <t>Jocelyn Wang</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -8918,22 +8918,22 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
+          <t>USENIX_SECURITY-Websites' Global Privacy Control Compliance at Scale and over Time.</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Carolina Ortega Pérez</t>
+          <t>Julia Netter</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Encrypted Access Logging for Online Accounts: Device Attributions without Device Tracking.</t>
+          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -8949,14 +8949,14 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Alaa Daffalla</t>
+          <t>Tim Nelson</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Encrypted Access Logging for Online Accounts: Device Attributions without Device Tracking.</t>
+          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -8972,14 +8972,14 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Yevgeniy Dodis</t>
+          <t>Skyler Austen</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -8987,22 +8987,22 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-How to Compare Bandwidth Constrained Two-Party Secure Messaging Protocols: A Quest for A More Efficient and Secure Post-Quantum Protocol.</t>
+          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Daniel Jost 0001</t>
+          <t>Eva Lau</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -9010,22 +9010,22 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-How to Compare Bandwidth Constrained Two-Party Secure Messaging Protocols: A Quest for A More Efficient and Secure Post-Quantum Protocol.</t>
+          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Tongwei Ren</t>
+          <t>Colton Rusch</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -9033,22 +9033,22 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
+          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Ronghan Che</t>
+          <t>Malte Schwarzkopf</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -9056,22 +9056,22 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
+          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Robert J. Walls</t>
+          <t>Kathi Fisler</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -9079,22 +9079,22 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
+          <t>USENIX_SECURITY-A Stakeholder-Based Framework to Highlight Tensions when Implementing Privacy Features.</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Jay Bosamiya</t>
+          <t>Carolina Ortega Pérez</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
+          <t>USENIX_SECURITY-Encrypted Access Logging for Online Accounts: Device Attributions without Device Tracking.</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -9110,14 +9110,14 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Microsoft Research</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Maverick Woo</t>
+          <t>Alaa Daffalla</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
+          <t>USENIX_SECURITY-Encrypted Access Logging for Online Accounts: Device Attributions without Device Tracking.</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -9133,14 +9133,14 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Bryan Parno</t>
+          <t>Yevgeniy Dodis</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -9148,22 +9148,22 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
+          <t>USENIX_SECURITY-How to Compare Bandwidth Constrained Two-Party Secure Messaging Protocols: A Quest for A More Efficient and Secure Post-Quantum Protocol.</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Yi Cai</t>
+          <t>Daniel Jost 0001</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -9171,22 +9171,22 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
+          <t>USENIX_SECURITY-How to Compare Bandwidth Constrained Two-Party Secure Messaging Protocols: A Quest for A More Efficient and Secure Post-Quantum Protocol.</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Pratap Singh</t>
+          <t>Tongwei Ren</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -9194,22 +9194,22 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
+          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Zhengyao Lin</t>
+          <t>Ronghan Che</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -9217,22 +9217,22 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
+          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Jay Bosamiya</t>
+          <t>Guin Gilman</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -9240,22 +9240,22 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
+          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Microsoft Research</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Joshua Gancher</t>
+          <t>Robert J. Walls</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
+          <t>USENIX_SECURITY-REVDECODE: Enhancing Binary Function Matching with Context-Aware Graph Representations and Relevance Decoding.</t>
         </is>
       </c>
       <c r="D385" t="n">
@@ -9271,14 +9271,14 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Milijana Surbatovich</t>
+          <t>Jay Bosamiya</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -9286,22 +9286,22 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
+          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Microsoft Research</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Bryan Parno</t>
+          <t>Maverick Woo</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -9309,11 +9309,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
+          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Sai Ritvik Tanksalkar</t>
+          <t>Bryan Parno</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -9332,22 +9332,22 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
+          <t>USENIX_SECURITY-TRex: Practical Type Reconstruction for Binary Code.</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Siddharth Muralee</t>
+          <t>Yi Cai</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -9355,22 +9355,22 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
+          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Srihari Danduri</t>
+          <t>Pratap Singh</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -9378,22 +9378,22 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
+          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Antonio Bianchi</t>
+          <t>Zhengyao Lin</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -9401,22 +9401,22 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
+          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>James C. Davis 0001</t>
+          <t>Jay Bosamiya</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -9424,22 +9424,22 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
+          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Microsoft Research</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Aravind Kumar Machiry</t>
+          <t>Joshua Gancher</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -9447,22 +9447,22 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
+          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Hung-Mao Chen</t>
+          <t>Milijana Surbatovich</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -9470,22 +9470,22 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
+          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Xu He</t>
+          <t>Bryan Parno</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -9493,22 +9493,22 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
+          <t>USENIX_SECURITY-Vest: Verified, Secure, High-Performance Parsing and Serialization for Rust.</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Shu Wang 0004</t>
+          <t>Sai Ritvik Tanksalkar</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -9516,22 +9516,22 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
+          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>George Mason University and Palo Alto Networks, Inc.</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Xiaokuan Zhang</t>
+          <t>Siddharth Muralee</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -9539,22 +9539,22 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
+          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Kun Sun 0001</t>
+          <t>Srihari Danduri</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -9562,22 +9562,22 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
+          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Andrew Bao</t>
+          <t>Paschal C. Amusuo</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -9585,22 +9585,22 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
+          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>University of Minnesota, Twin Cities</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Stephen McCamant</t>
+          <t>Antonio Bianchi</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
+          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -9616,14 +9616,14 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>University of Minnesota, Twin Cities</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Pen-Chung Yew</t>
+          <t>James C. Davis 0001</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
+          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -9639,14 +9639,14 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>University of Minnesota, Twin Cities</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Murtuza Jadliwala</t>
+          <t>Aravind Kumar Machiry</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -9654,22 +9654,22 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-LightShed: Defeating Perturbation-based Image Copyright Protections.</t>
+          <t>USENIX_SECURITY-LEMIX: Enabling Testing of Embedded Applications as Linux Applications.</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>University of Texas at San Antonio</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Minhao Jin</t>
+          <t>Hung-Mao Chen</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Robustifying ML-powered Network Classifiers with PANTS.</t>
+          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -9685,14 +9685,14 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Maria Apostolaki</t>
+          <t>Xu He</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Robustifying ML-powered Network Classifiers with PANTS.</t>
+          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -9708,14 +9708,14 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Chenyi Wang 0005</t>
+          <t>Shu Wang 0004</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -9723,22 +9723,22 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
+          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>George Mason University and Palo Alto Networks, Inc.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Raymond Muller</t>
+          <t>Xiaokuan Zhang</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
+          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Ruoyu Song 0001</t>
+          <t>Kun Sun 0001</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -9769,22 +9769,22 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
+          <t>USENIX_SECURITY-TYPEPULSE: Detecting Type Confusion Bugs in Rust Programs.</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Jean-Philippe Monteuuis</t>
+          <t>Andrew Bao</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
+          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Jonathan Petit</t>
+          <t>Stephen McCamant</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
+          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
         </is>
       </c>
       <c r="D409" t="n">
@@ -9823,14 +9823,14 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>Pen-Chung Yew</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
+          <t>USENIX_SECURITY-From Alarms to Real Bugs: Multi-target Multi-step Directed Greybox Fuzzing for Static Analysis Result Verification.</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Ming Li 0003</t>
+          <t>Murtuza Jadliwala</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -9861,22 +9861,22 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
+          <t>USENIX_SECURITY-LightShed: Defeating Perturbation-based Image Copyright Protections.</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>University of Texas at San Antonio</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Jennifer Miller</t>
+          <t>Minhao Jin</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-Robustifying ML-powered Network Classifiers with PANTS.</t>
         </is>
       </c>
       <c r="D412" t="n">
@@ -9892,14 +9892,14 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Manas Ghandat</t>
+          <t>Maria Apostolaki</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-Robustifying ML-powered Network Classifiers with PANTS.</t>
         </is>
       </c>
       <c r="D413" t="n">
@@ -9915,14 +9915,14 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Kyle Zeng</t>
+          <t>Chenyi Wang 0005</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -9930,22 +9930,22 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Hongkai Chen</t>
+          <t>Raymond Muller</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -9953,22 +9953,22 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Tiffany Bao</t>
+          <t>Ruoyu Song 0001</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -9976,22 +9976,22 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Ruoyu Wang 0001</t>
+          <t>Jean-Philippe Monteuuis</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -9999,22 +9999,22 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Qualcomm</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Adam Doupé</t>
+          <t>Jonathan Petit</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -10022,22 +10022,22 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Qualcomm</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Yan Shoshitaishvili</t>
+          <t>Ryan M. Gerdes</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -10045,22 +10045,22 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Yue Zhang 0025</t>
+          <t>Z. Berkay Celik</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -10068,22 +10068,22 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The Cost of Performance: Breaking ThreadX with Kernel Object Masquerading Attacks.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Drexel University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Xinwen Fu</t>
+          <t>Ming Li 0003</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The Cost of Performance: Breaking ThreadX with Kernel Object Masquerading Attacks.</t>
+          <t>USENIX_SECURITY-From Threat to Trust: Exploiting Attention Mechanisms for Attacks and Defenses in Cooperative Perception.</t>
         </is>
       </c>
       <c r="D421" t="n">
@@ -10099,14 +10099,14 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>University of Massachusetts Lowell</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Wojciech Ozga</t>
+          <t>Jennifer Miller</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -10114,22 +10114,22 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Save what must be saved: Secure context switching with Sailor.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>IBM Research - Zurich</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Tianyao Gu</t>
+          <t>Manas Ghandat</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -10137,22 +10137,22 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Afonso Tinoco</t>
+          <t>Kyle Zeng</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D424" t="n">
@@ -10168,14 +10168,14 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Elaine Shi</t>
+          <t>Hongkai Chen</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -10183,22 +10183,22 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Xinwen Fu</t>
+          <t>Abdelouahab Benchikh</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -10206,22 +10206,22 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Distributed Private Aggregation in Graph Neural Networks.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>University of Massachusetts Lowell</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>David Froelicher</t>
+          <t>Tiffany Bao</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -10229,22 +10229,22 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Bonnie Berger</t>
+          <t>Ruoyu Wang 0001</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -10252,22 +10252,22 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Hyunghoon Cho</t>
+          <t>Adam Doupé</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -10275,22 +10275,22 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Mazharul Islam 0002</t>
+          <t>Yan Shoshitaishvili</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -10298,22 +10298,22 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
+          <t>USENIX_SECURITY-System Register Hijacking: Compromising Kernel Integrity By Turning System Registers Against the System.</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>University of Wisconsin—Madison</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Sunpreet S. Arora</t>
+          <t>Yue Zhang 0025</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -10321,22 +10321,22 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
+          <t>USENIX_SECURITY-The Cost of Performance: Breaking ThreadX with Kernel Object Masquerading Attacks.</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Visa Research</t>
+          <t>Drexel University</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Rahul Chatterjee 0001</t>
+          <t>Xinwen Fu</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -10344,22 +10344,22 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
+          <t>USENIX_SECURITY-The Cost of Performance: Breaking ThreadX with Kernel Object Masquerading Attacks.</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>University of Wisconsin—Madison</t>
+          <t>University of Massachusetts Lowell</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Ke Coby Wang</t>
+          <t>Wojciech Ozga</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
+          <t>USENIX_SECURITY-Save what must be saved: Secure context switching with Sailor.</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -10375,14 +10375,14 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Visa Research</t>
+          <t>IBM Research - Zurich</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Alaa Daffalla</t>
+          <t>Tianyao Gu</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
+          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
         </is>
       </c>
       <c r="D434" t="n">
@@ -10398,14 +10398,14 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Arkaprabha Bhattacharya</t>
+          <t>Afonso Tinoco</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -10413,22 +10413,22 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
+          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Rahul Chatterjee 0001</t>
+          <t>Elaine Shi</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -10436,22 +10436,22 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
+          <t>USENIX_SECURITY-Flexway O-Sort: Enclave-Friendly and Optimal Oblivious Sorting.</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>University of Wisconsin—Madison</t>
+          <t>Carnegie Mellon University and Oblivious Labs Inc.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Nicola Dell</t>
+          <t>Xinwen Fu</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -10459,22 +10459,22 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
+          <t>USENIX_SECURITY-Distributed Private Aggregation in Graph Neural Networks.</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Cornell Tech</t>
+          <t>University of Massachusetts Lowell</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Rosanna Bellini</t>
+          <t>David Froelicher</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -10482,22 +10482,22 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
+          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Thomas Ristenpart</t>
+          <t>Bonnie Berger</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -10505,22 +10505,22 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
+          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Cornell Tech</t>
+          <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Yuchen Yang 0001</t>
+          <t>Hyunghoon Cho</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -10528,22 +10528,22 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
+          <t>USENIX_SECURITY-Shechi: A Secure Distributed Computation Compiler Based on Multiparty Homomorphic Encryption.</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>The Johns Hopkins University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Qichang Liu</t>
+          <t>Mazharul Islam 0002</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -10551,22 +10551,22 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
+          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>The Johns Hopkins University</t>
+          <t>University of Wisconsin—Madison</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Huan Zhang 0001</t>
+          <t>Sunpreet S. Arora</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -10574,22 +10574,22 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
+          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>University of Illinois at Urbana–Champaign</t>
+          <t>Visa Research</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Rahul Chatterjee 0001</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -10597,22 +10597,22 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
+          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>University of Wisconsin—Madison</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Gene Tsudik</t>
+          <t>Ke Coby Wang</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -10620,22 +10620,22 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Oblivious Digital Tokens.</t>
+          <t>USENIX_SECURITY-Detecting Compromise of Passkey Storage on the Cloud.</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>Visa Research</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>John Y. Kim</t>
+          <t>Alaa Daffalla</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
+          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -10651,14 +10651,14 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Chaoshun Zuo</t>
+          <t>Arkaprabha Bhattacharya</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
+          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
         </is>
       </c>
       <c r="D446" t="n">
@@ -10674,14 +10674,14 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Ohio State University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Rahul Chatterjee 0001</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
+          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
         </is>
       </c>
       <c r="D447" t="n">
@@ -10697,14 +10697,14 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>University of Wisconsin—Madison</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Grace Jia</t>
+          <t>Nicola Dell</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -10712,22 +10712,22 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
+          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Cornell Tech</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Alex Wong 0001</t>
+          <t>Rosanna Bellini</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -10735,22 +10735,22 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
+          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Anurag Khandelwal</t>
+          <t>Thomas Ristenpart</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -10758,22 +10758,22 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
+          <t>USENIX_SECURITY-A Framework for Abusability Analysis: The Case of Passkeys in Interpersonal Threat Models.</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Cornell Tech</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Yash Vekaria</t>
+          <t>Yuchen Yang 0001</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
+          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
         </is>
       </c>
       <c r="D451" t="n">
@@ -10789,14 +10789,14 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>The Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Jonathan Levitsky</t>
+          <t>Qichang Liu</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -10804,22 +10804,22 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
+          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>The Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Zubair Shafiq</t>
+          <t>Huan Zhang 0001</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -10827,22 +10827,22 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
+          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>University of Illinois at Urbana–Champaign</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Kaiyuan Zhang 0002</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -10850,22 +10850,22 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-CertPHash: Towards Certified Perceptual Hashing via Robust Training.</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Siyuan Cheng 0005</t>
+          <t>Gene Tsudik</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -10873,22 +10873,22 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-Oblivious Digital Tokens.</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>UC Irvine</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Hanxi Guo</t>
+          <t>John Y. Kim</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -10896,22 +10896,22 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Yuetian Chen</t>
+          <t>Chaoshun Zuo</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -10919,22 +10919,22 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Zian Su</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -10942,22 +10942,22 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-AUTOVR: Automated UI Exploration for Detecting Sensitive Data Flow Exposures in Virtual Reality Apps.</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Shengwei An</t>
+          <t>Grace Jia</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -10965,22 +10965,22 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Yuntao Du 0002</t>
+          <t>Alex Wong 0001</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -10988,22 +10988,22 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Xiangyu Zhang 0001</t>
+          <t>Anurag Khandelwal</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -11011,22 +11011,22 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-Found in Translation: A Generative Language Modeling Approach to Memory Access Pattern Attacks.</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Ninghui Li 0001</t>
+          <t>Yash Vekaria</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -11034,22 +11034,22 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
+          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>UC Davis</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Leo Marchyok</t>
+          <t>Jonathan Levitsky</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Private Investigator: Extracting Personally Identifiable Information from Large Language Models Using Optimized Prompts.</t>
+          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
         </is>
       </c>
       <c r="D463" t="n">
@@ -11065,14 +11065,14 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>UC Davis</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Sanghyun Hong 0001</t>
+          <t>Zubair Shafiq</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -11080,22 +11080,22 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Private Investigator: Extracting Personally Identifiable Information from Large Language Models Using Optimized Prompts.</t>
+          <t>USENIX_SECURITY-Big Help or Big Brother? Auditing Tracking, Profiling, and Personalization in Generative AI Assistants.</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>UC Davis</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Zhengyu Liu</t>
+          <t>Kaiyuan Zhang 0002</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D465" t="n">
@@ -11111,14 +11111,14 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Theo Lee</t>
+          <t>Siyuan Cheng 0005</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D466" t="n">
@@ -11134,14 +11134,14 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Jianjia Yu</t>
+          <t>Hanxi Guo</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D467" t="n">
@@ -11157,14 +11157,14 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Zifeng Kang</t>
+          <t>Yuetian Chen</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -11180,14 +11180,14 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Zian Su</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D469" t="n">
@@ -11203,14 +11203,14 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Rigel Gjomemo</t>
+          <t>Shengwei An</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -11218,22 +11218,22 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-FIXX: FInding eXploits from eXamples.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Yuntao Du 0002</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -11241,22 +11241,22 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Careless Retention and Management: Understanding and Detecting Data Retention Denial-of-Service Vulnerabilities in Java Web Containers.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Xiangyu Zhang 0001</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -11264,22 +11264,22 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Towards Automatic Detection and Exploitation of Java Web Application Vulnerabilities via Concolic Execution guided by Cross-thread Object Manipulation.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Yunhao Wang</t>
+          <t>Ninghui Li 0001</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -11287,22 +11287,22 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Qelect: Lattice-based Single Secret Leader Election Made Practical.</t>
+          <t>USENIX_SECURITY-SOFT: Selective Data Obfuscation for Protecting LLM Fine-tuning against Membership Inference Attacks.</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Fan Zhang</t>
+          <t>Leo Marchyok</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -11310,22 +11310,22 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-Qelect: Lattice-based Single Secret Leader Election Made Practical.</t>
+          <t>USENIX_SECURITY-Private Investigator: Extracting Personally Identifiable Information from Large Language Models Using Optimized Prompts.</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Oregon State University</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Lakshmi Likhitha Mankali</t>
+          <t>Sanghyun Hong 0001</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+          <t>USENIX_SECURITY-Private Investigator: Extracting Personally Identifiable Information from Large Language Models Using Optimized Prompts.</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Tandon School of Engineering, New York University</t>
+          <t>Oregon State University</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Mohammed Nabeel 0001</t>
+          <t>Zhengyu Liu</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -11356,22 +11356,22 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Tandon School of Engineering, New York University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Faiq Raees</t>
+          <t>Theo Lee</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -11379,22 +11379,22 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Michail Maniatakos</t>
+          <t>Jianjia Yu</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -11402,22 +11402,22 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Ozgur Sinanoglu</t>
+          <t>Zifeng Kang</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -11425,22 +11425,22 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Johann Knechtel</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -11448,22 +11448,22 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+          <t>USENIX_SECURITY-The DOMino Effect: Detecting and Exploiting DOM Clobbering Gadgets via Concolic Execution with Symbolic DOM.</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>New York University Abu Dhabi</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Apostolos Mavrogiannakis</t>
+          <t>Neil P. Thimmaiah</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>USENIX_SECURITY-OBLIVIATOR: OBLIVIous Parallel Joins and other OperATORs in Shared Memory Environments.</t>
+          <t>USENIX_SECURITY-FIXX: FInding eXploits from eXamples.</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -11479,28 +11479,350 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
+          <t>Yashashvi J. Dave</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-FIXX: FInding eXploits from eXamples.</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>1</v>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Rigel Gjomemo</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-FIXX: FInding eXploits from eXamples.</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>2</v>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>V. N. Venkatakrishnan</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-FIXX: FInding eXploits from eXamples.</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>3</v>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Yinzhi Cao</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-Careless Retention and Management: Understanding and Detecting Data Retention Denial-of-Service Vulnerabilities in Java Web Containers.</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>3</v>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Yinzhi Cao</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-Towards Automatic Detection and Exploitation of Java Web Application Vulnerabilities via Concolic Execution guided by Cross-thread Object Manipulation.</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>4</v>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Yunhao Wang</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-Qelect: Lattice-based Single Secret Leader Election Made Practical.</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>0</v>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Yale University</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Fan Zhang</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-Qelect: Lattice-based Single Secret Leader Election Made Practical.</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>1</v>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Yale University</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Lakshmi Likhitha Mankali</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>0</v>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Tandon School of Engineering, New York University</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Mohammed Nabeel 0001</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>1</v>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Tandon School of Engineering, New York University</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Faiq Raees</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>2</v>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Michail Maniatakos</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>3</v>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>New York University Abu Dhabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Ozgur Sinanoglu</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>4</v>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>New York University Abu Dhabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Johann Knechtel</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-GlitchFHE: Attacking Fully Homomorphic Encryption Using Fault Injection.</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>5</v>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>New York University Abu Dhabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Apostolos Mavrogiannakis</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>USENIX_SECURITY-OBLIVIATOR: OBLIVIous Parallel Joins and other OperATORs in Shared Memory Environments.</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>0</v>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>University of California, Santa Cruz</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
           <t>Ioannis Demertzis</t>
         </is>
       </c>
-      <c r="B482" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C482" t="inlineStr">
+      <c r="B496" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C496" t="inlineStr">
         <is>
           <t>USENIX_SECURITY-OBLIVIATOR: OBLIVIous Parallel Joins and other OperATORs in Shared Memory Environments.</t>
         </is>
       </c>
-      <c r="D482" t="n">
+      <c r="D496" t="n">
         <v>2</v>
       </c>
-      <c r="E482" t="inlineStr">
+      <c r="E496" t="inlineStr">
         <is>
           <t>University of California, Santa Cruz</t>
         </is>
